--- a/data/research.xlsx
+++ b/data/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM67" headerRowCount="1">
-  <autoFilter ref="A1:CM67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM70" headerRowCount="1">
+  <autoFilter ref="A1:CM70"/>
   <tableColumns count="91">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -750,19 +750,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$67)</f>
+        <f>COUNTA('Picks'!$A$2:$A$70)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$70,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$70,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")+COUNTIFS('Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -790,19 +790,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$67,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$70,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")/(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"win")/(COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"win")+COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$67)/SUM('Picks'!$BX$2:$BX$67),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$70)/SUM('Picks'!$BX$2:$BX$70),0)</f>
         <v/>
       </c>
     </row>
@@ -830,19 +830,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$67)</f>
+        <f>SUM('Picks'!$BY$2:$BY$70)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$67,"&lt;&gt;",'Picks'!$AB$2:$AB$67),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$70,"&lt;&gt;",'Picks'!$AB$2:$AB$70),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$70,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$70,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$67,'Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$70,'Picks'!$AM$2:$AM$70,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -913,11 +913,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$70,'Picks'!$H$2:$H$70,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$70,'Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -928,15 +928,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -944,11 +944,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$70,'Picks'!$H$2:$H$70,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$70,'Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -975,11 +975,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$70,'Picks'!$H$2:$H$70,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$70,'Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CM67"/>
+  <dimension ref="A1:CM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1644,18 +1644,32 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:06:47.377520Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-jdg-al-2026-07-23).</t>
@@ -2688,18 +2702,32 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:06:48.952359Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-re-ent-2026-07-23).</t>
@@ -2949,18 +2977,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:06:50.239968Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-nve-bge-2026-07-23).</t>
@@ -2973,7 +3015,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3210,18 +3252,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:06:51.764225Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-lav-erx-2026-07-23).</t>
@@ -6603,18 +6659,32 @@
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:06:58.686176Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-ge-fs-2026-07-23).</t>
@@ -9474,18 +9544,32 @@
       </c>
       <c r="U32" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
-      <c r="AD32" s="24" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:04.630750Z</t>
+        </is>
+      </c>
       <c r="AE32" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-jdg-al-2026-07-23).</t>
@@ -11301,18 +11385,32 @@
       </c>
       <c r="U39" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y39" s="25" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
+      <c r="AC39" s="30" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="AD39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:06.071632Z</t>
+        </is>
+      </c>
       <c r="AE39" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-re-ent-2026-07-23).</t>
@@ -11562,18 +11660,32 @@
       </c>
       <c r="U40" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y40" s="25" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
+      <c r="AC40" s="30" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="AD40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:07.369963Z</t>
+        </is>
+      </c>
       <c r="AE40" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-lk-sawy-2026-07-23).</t>
@@ -11823,18 +11935,32 @@
       </c>
       <c r="U41" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y41" s="25" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
+      <c r="AC41" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:08.386274Z</t>
+        </is>
+      </c>
       <c r="AE41" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-nve-bge-2026-07-23).</t>
@@ -11847,7 +11973,7 @@
       </c>
       <c r="AG41" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH41" s="24" t="n"/>
@@ -12084,18 +12210,32 @@
       </c>
       <c r="U42" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y42" s="25" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
+      <c r="AC42" s="30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:09.429767Z</t>
+        </is>
+      </c>
       <c r="AE42" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-lav-erx-2026-07-23).</t>
@@ -12345,18 +12485,32 @@
       </c>
       <c r="U43" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y43" s="25" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
+      <c r="AC43" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD43" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:10.792030Z</t>
+        </is>
+      </c>
       <c r="AE43" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-wal-3dmax-2026-07-23).</t>
@@ -12369,7 +12523,7 @@
       </c>
       <c r="AG43" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH43" s="24" t="n"/>
@@ -12867,18 +13021,32 @@
       </c>
       <c r="U45" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y45" s="25" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
+      <c r="AC45" s="30" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:13.285054Z</t>
+        </is>
+      </c>
       <c r="AE45" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-uno-gh-2026-07-23).</t>
@@ -16260,18 +16428,32 @@
       </c>
       <c r="U58" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V58" s="24" t="n"/>
-      <c r="W58" s="26" t="n"/>
-      <c r="X58" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y58" s="25" t="n"/>
       <c r="Z58" s="26" t="n"/>
       <c r="AA58" s="28" t="n"/>
       <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n"/>
-      <c r="AD58" s="24" t="n"/>
+      <c r="AC58" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD58" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:15.944958Z</t>
+        </is>
+      </c>
       <c r="AE58" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-tsa-pckcp-2026-07-23).</t>
@@ -16284,7 +16466,7 @@
       </c>
       <c r="AG58" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH58" s="24" t="n"/>
@@ -17043,18 +17225,32 @@
       </c>
       <c r="U61" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V61" s="24" t="n"/>
-      <c r="W61" s="26" t="n"/>
-      <c r="X61" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V61" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y61" s="25" t="n"/>
       <c r="Z61" s="26" t="n"/>
       <c r="AA61" s="28" t="n"/>
       <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n"/>
-      <c r="AD61" s="24" t="n"/>
+      <c r="AC61" s="30" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AD61" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:18.094700Z</t>
+        </is>
+      </c>
       <c r="AE61" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-ge-fs-2026-07-23).</t>
@@ -17304,18 +17500,32 @@
       </c>
       <c r="U62" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V62" s="24" t="n"/>
-      <c r="W62" s="26" t="n"/>
-      <c r="X62" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V62" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W62" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y62" s="25" t="n"/>
       <c r="Z62" s="26" t="n"/>
       <c r="AA62" s="28" t="n"/>
       <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
-      <c r="AD62" s="24" t="n"/>
+      <c r="AC62" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD62" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:07:19.415989Z</t>
+        </is>
+      </c>
       <c r="AE62" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-tyloo-nova-2026-07-23).</t>
@@ -17328,7 +17538,7 @@
       </c>
       <c r="AG62" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH62" s="24" t="n"/>
@@ -18787,6 +18997,783 @@
       <c r="CL67" s="24" t="n"/>
       <c r="CM67" s="24" t="n"/>
     </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>18112a8aa3e94c75</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:36:56.355200Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>57087</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J68" s="25" t="n"/>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M68" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.509073</v>
+      </c>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="28" t="n">
+        <v>0.009072999999999999</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="25" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="30" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-aee-zena-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:36:35.822840Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="25" t="n"/>
+      <c r="BK68" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL68" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN68" s="28" t="n"/>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="25" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+      <c r="CB68" s="24" t="n"/>
+      <c r="CC68" s="24" t="n"/>
+      <c r="CD68" s="24" t="n"/>
+      <c r="CE68" s="24" t="n"/>
+      <c r="CF68" s="24" t="n"/>
+      <c r="CG68" s="24" t="n"/>
+      <c r="CH68" s="24" t="n"/>
+      <c r="CI68" s="24" t="n"/>
+      <c r="CJ68" s="24" t="n"/>
+      <c r="CK68" s="24" t="n"/>
+      <c r="CL68" s="24" t="n"/>
+      <c r="CM68" s="24" t="n"/>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>b1ce021bdf954f06</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:36:56.355200Z</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>57173</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J69" s="25" t="n"/>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M69" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O69" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="28" t="n">
+        <v>0.019231</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S69" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T69" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U69" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="25" t="n"/>
+      <c r="Z69" s="26" t="n"/>
+      <c r="AA69" s="28" t="n"/>
+      <c r="AB69" s="28" t="n"/>
+      <c r="AC69" s="30" t="n"/>
+      <c r="AD69" s="24" t="n"/>
+      <c r="AE69" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-piv-ds-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF69" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG69" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH69" s="24" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL69" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN69" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO69" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP69" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="AQ69" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="AR69" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="AS69" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AT69" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AU69" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AV69" s="24" t="n"/>
+      <c r="AW69" s="24" t="n"/>
+      <c r="AX69" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY69" s="24" t="n"/>
+      <c r="AZ69" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA69" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BB69" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC69" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD69" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BE69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG69" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:36:41.613196Z</t>
+        </is>
+      </c>
+      <c r="BI69" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ69" s="25" t="n"/>
+      <c r="BK69" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL69" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM69" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN69" s="28" t="n"/>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="25" t="n"/>
+      <c r="BQ69" s="27" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
+      <c r="BT69" s="28" t="n"/>
+      <c r="BU69" s="25" t="n"/>
+      <c r="BV69" s="29" t="n"/>
+      <c r="BW69" s="24" t="n"/>
+      <c r="BX69" s="30" t="n"/>
+      <c r="BY69" s="27" t="n"/>
+      <c r="BZ69" s="24" t="n"/>
+      <c r="CA69" s="31" t="n"/>
+      <c r="CB69" s="24" t="n"/>
+      <c r="CC69" s="24" t="n"/>
+      <c r="CD69" s="24" t="n"/>
+      <c r="CE69" s="24" t="n"/>
+      <c r="CF69" s="24" t="n"/>
+      <c r="CG69" s="24" t="n"/>
+      <c r="CH69" s="24" t="n"/>
+      <c r="CI69" s="24" t="n"/>
+      <c r="CJ69" s="24" t="n"/>
+      <c r="CK69" s="24" t="n"/>
+      <c r="CL69" s="24" t="n"/>
+      <c r="CM69" s="24" t="n"/>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>8df8d2a46c0445a8</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:36:56.355200Z</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>57214</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J70" s="25" t="n"/>
+      <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M70" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N70" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O70" s="28" t="n">
+        <v>0.552791</v>
+      </c>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="28" t="n">
+        <v>0.172563</v>
+      </c>
+      <c r="R70" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S70" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U70" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V70" s="24" t="n"/>
+      <c r="W70" s="26" t="n"/>
+      <c r="X70" s="26" t="n"/>
+      <c r="Y70" s="25" t="n"/>
+      <c r="Z70" s="26" t="n"/>
+      <c r="AA70" s="28" t="n"/>
+      <c r="AB70" s="28" t="n"/>
+      <c r="AC70" s="30" t="n"/>
+      <c r="AD70" s="24" t="n"/>
+      <c r="AE70" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-cg-hmble-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF70" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG70" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH70" s="24" t="n"/>
+      <c r="AI70" s="31" t="n"/>
+      <c r="AJ70" s="31" t="n"/>
+      <c r="AK70" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM70" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN70" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO70" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP70" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AQ70" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AR70" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AS70" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="AT70" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="AU70" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="AV70" s="24" t="n"/>
+      <c r="AW70" s="24" t="n"/>
+      <c r="AX70" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY70" s="24" t="n"/>
+      <c r="AZ70" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA70" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BB70" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC70" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD70" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BE70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG70" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH70" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:36:44.095489Z</t>
+        </is>
+      </c>
+      <c r="BI70" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ70" s="25" t="n"/>
+      <c r="BK70" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL70" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM70" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN70" s="28" t="n"/>
+      <c r="BO70" s="28" t="n"/>
+      <c r="BP70" s="25" t="n"/>
+      <c r="BQ70" s="27" t="n"/>
+      <c r="BR70" s="28" t="n"/>
+      <c r="BS70" s="28" t="n"/>
+      <c r="BT70" s="28" t="n"/>
+      <c r="BU70" s="25" t="n"/>
+      <c r="BV70" s="29" t="n"/>
+      <c r="BW70" s="24" t="n"/>
+      <c r="BX70" s="30" t="n"/>
+      <c r="BY70" s="27" t="n"/>
+      <c r="BZ70" s="24" t="n"/>
+      <c r="CA70" s="31" t="n"/>
+      <c r="CB70" s="24" t="n"/>
+      <c r="CC70" s="24" t="n"/>
+      <c r="CD70" s="24" t="n"/>
+      <c r="CE70" s="24" t="n"/>
+      <c r="CF70" s="24" t="n"/>
+      <c r="CG70" s="24" t="n"/>
+      <c r="CH70" s="24" t="n"/>
+      <c r="CI70" s="24" t="n"/>
+      <c r="CJ70" s="24" t="n"/>
+      <c r="CK70" s="24" t="n"/>
+      <c r="CL70" s="24" t="n"/>
+      <c r="CM70" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research.xlsx
+++ b/data/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM70" headerRowCount="1">
-  <autoFilter ref="A1:CM70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM77" headerRowCount="1">
+  <autoFilter ref="A1:CM77"/>
   <tableColumns count="91">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -750,19 +750,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$70)</f>
+        <f>COUNTA('Picks'!$A$2:$A$77)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$70,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$77,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$70,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")+COUNTIFS('Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")+COUNTIFS('Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -790,19 +790,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$70,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$77,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"win")/(COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"win")+COUNTIFS('Picks'!$BX$2:$BX$70,"&gt;0",'Picks'!$V$2:$V$70,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")/(COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")+COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$70)/SUM('Picks'!$BX$2:$BX$70),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$77)/SUM('Picks'!$BX$2:$BX$77),0)</f>
         <v/>
       </c>
     </row>
@@ -830,19 +830,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$70)</f>
+        <f>SUM('Picks'!$BY$2:$BY$77)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$70,"&lt;&gt;",'Picks'!$AB$2:$AB$70),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$77,"&lt;&gt;",'Picks'!$AB$2:$AB$77),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$70,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$70,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$77,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$70,'Picks'!$AM$2:$AM$70,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$77,'Picks'!$AM$2:$AM$77,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -913,11 +913,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$70,'Picks'!$H$2:$H$70,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$70,'Picks'!$H$2:$H$70,$A14,'Picks'!$U$2:$U$70,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -928,15 +928,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -944,11 +944,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$70,'Picks'!$H$2:$H$70,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$70,'Picks'!$H$2:$H$70,$A15,'Picks'!$U$2:$U$70,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled",'Picks'!$V$2:$V$70,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -975,11 +975,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$70,'Picks'!$H$2:$H$70,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$70,'Picks'!$H$2:$H$70,$A16,'Picks'!$U$2:$U$70,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CM70"/>
+  <dimension ref="A1:CM77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3788,18 +3788,32 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:15:36.106170Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-33-sparta-2026-07-23).</t>
@@ -3812,7 +3826,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -8500,18 +8514,32 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:15:41.948301Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-33-sparta-2026-07-23).</t>
@@ -8524,7 +8552,7 @@
       </c>
       <c r="AG28" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH28" s="24" t="n"/>
@@ -19774,6 +19802,1819 @@
       <c r="CL70" s="24" t="n"/>
       <c r="CM70" s="24" t="n"/>
     </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>468b935ae3ae48a3</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>52897</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J71" s="25" t="n"/>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M71" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>0.701777</v>
+      </c>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="28" t="n">
+        <v>0.061489</v>
+      </c>
+      <c r="R71" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S71" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="n"/>
+      <c r="W71" s="26" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="25" t="n"/>
+      <c r="Z71" s="26" t="n"/>
+      <c r="AA71" s="28" t="n"/>
+      <c r="AB71" s="28" t="n"/>
+      <c r="AC71" s="30" t="n"/>
+      <c r="AD71" s="24" t="n"/>
+      <c r="AE71" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-oldboyspl-gel-2026-07-16).</t>
+        </is>
+      </c>
+      <c r="AF71" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG71" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH71" s="24" t="n"/>
+      <c r="AI71" s="31" t="n"/>
+      <c r="AJ71" s="31" t="n"/>
+      <c r="AK71" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL71" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM71" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN71" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO71" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP71" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="AQ71" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="AR71" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="AS71" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AT71" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AU71" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AV71" s="24" t="n"/>
+      <c r="AW71" s="24" t="n"/>
+      <c r="AX71" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY71" s="24" t="n"/>
+      <c r="AZ71" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA71" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB71" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC71" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD71" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG71" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH71" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:03.102663Z</t>
+        </is>
+      </c>
+      <c r="BI71" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ71" s="25" t="n"/>
+      <c r="BK71" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL71" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM71" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN71" s="28" t="n"/>
+      <c r="BO71" s="28" t="n"/>
+      <c r="BP71" s="25" t="n"/>
+      <c r="BQ71" s="27" t="n"/>
+      <c r="BR71" s="28" t="n"/>
+      <c r="BS71" s="28" t="n"/>
+      <c r="BT71" s="28" t="n"/>
+      <c r="BU71" s="25" t="n"/>
+      <c r="BV71" s="29" t="n"/>
+      <c r="BW71" s="24" t="n"/>
+      <c r="BX71" s="30" t="n"/>
+      <c r="BY71" s="27" t="n"/>
+      <c r="BZ71" s="24" t="n"/>
+      <c r="CA71" s="31" t="n"/>
+      <c r="CB71" s="24" t="n"/>
+      <c r="CC71" s="24" t="n"/>
+      <c r="CD71" s="24" t="n"/>
+      <c r="CE71" s="24" t="n"/>
+      <c r="CF71" s="24" t="n"/>
+      <c r="CG71" s="24" t="n"/>
+      <c r="CH71" s="24" t="n"/>
+      <c r="CI71" s="24" t="n"/>
+      <c r="CJ71" s="24" t="n"/>
+      <c r="CK71" s="24" t="n"/>
+      <c r="CL71" s="24" t="n"/>
+      <c r="CM71" s="24" t="n"/>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>0403f65bd0ca4be6</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>59846</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>uust _esports</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J72" s="25" t="n"/>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M72" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N72" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O72" s="28" t="n">
+        <v>0.68532</v>
+      </c>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="28" t="n">
+        <v>0.195124</v>
+      </c>
+      <c r="R72" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S72" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T72" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U72" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V72" s="24" t="n"/>
+      <c r="W72" s="26" t="n"/>
+      <c r="X72" s="26" t="n"/>
+      <c r="Y72" s="25" t="n"/>
+      <c r="Z72" s="26" t="n"/>
+      <c r="AA72" s="28" t="n"/>
+      <c r="AB72" s="28" t="n"/>
+      <c r="AC72" s="30" t="n"/>
+      <c r="AD72" s="24" t="n"/>
+      <c r="AE72" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sng-uust-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF72" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG72" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH72" s="24" t="n"/>
+      <c r="AI72" s="31" t="n"/>
+      <c r="AJ72" s="31" t="n"/>
+      <c r="AK72" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM72" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN72" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO72" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP72" s="24" t="inlineStr">
+        <is>
+          <t>uust _esports</t>
+        </is>
+      </c>
+      <c r="AQ72" s="24" t="inlineStr">
+        <is>
+          <t>uust _esports</t>
+        </is>
+      </c>
+      <c r="AR72" s="24" t="inlineStr">
+        <is>
+          <t>uust _esports</t>
+        </is>
+      </c>
+      <c r="AS72" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AT72" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AU72" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AV72" s="24" t="n"/>
+      <c r="AW72" s="24" t="n"/>
+      <c r="AX72" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY72" s="24" t="n"/>
+      <c r="AZ72" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA72" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB72" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC72" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD72" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG72" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH72" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:04.761269Z</t>
+        </is>
+      </c>
+      <c r="BI72" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ72" s="25" t="n"/>
+      <c r="BK72" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL72" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM72" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN72" s="28" t="n"/>
+      <c r="BO72" s="28" t="n"/>
+      <c r="BP72" s="25" t="n"/>
+      <c r="BQ72" s="27" t="n"/>
+      <c r="BR72" s="28" t="n"/>
+      <c r="BS72" s="28" t="n"/>
+      <c r="BT72" s="28" t="n"/>
+      <c r="BU72" s="25" t="n"/>
+      <c r="BV72" s="29" t="n"/>
+      <c r="BW72" s="24" t="n"/>
+      <c r="BX72" s="30" t="n"/>
+      <c r="BY72" s="27" t="n"/>
+      <c r="BZ72" s="24" t="n"/>
+      <c r="CA72" s="31" t="n"/>
+      <c r="CB72" s="24" t="n"/>
+      <c r="CC72" s="24" t="n"/>
+      <c r="CD72" s="24" t="n"/>
+      <c r="CE72" s="24" t="n"/>
+      <c r="CF72" s="24" t="n"/>
+      <c r="CG72" s="24" t="n"/>
+      <c r="CH72" s="24" t="n"/>
+      <c r="CI72" s="24" t="n"/>
+      <c r="CJ72" s="24" t="n"/>
+      <c r="CK72" s="24" t="n"/>
+      <c r="CL72" s="24" t="n"/>
+      <c r="CM72" s="24" t="n"/>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>131bb540d9bb4e21</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>59890</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>MTX</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J73" s="25" t="n"/>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M73" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O73" s="28" t="n">
+        <v>0.7052</v>
+      </c>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="28" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="R73" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S73" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T73" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U73" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V73" s="24" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
+      <c r="Y73" s="25" t="n"/>
+      <c r="Z73" s="26" t="n"/>
+      <c r="AA73" s="28" t="n"/>
+      <c r="AB73" s="28" t="n"/>
+      <c r="AC73" s="30" t="n"/>
+      <c r="AD73" s="24" t="n"/>
+      <c r="AE73" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-cs2-oldboyspl-mtx-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF73" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG73" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH73" s="24" t="n"/>
+      <c r="AI73" s="31" t="n"/>
+      <c r="AJ73" s="31" t="n"/>
+      <c r="AK73" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL73" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM73" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN73" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO73" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP73" s="24" t="inlineStr">
+        <is>
+          <t>MTX</t>
+        </is>
+      </c>
+      <c r="AQ73" s="24" t="inlineStr">
+        <is>
+          <t>MTX</t>
+        </is>
+      </c>
+      <c r="AR73" s="24" t="inlineStr">
+        <is>
+          <t>MTX</t>
+        </is>
+      </c>
+      <c r="AS73" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AT73" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AU73" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AV73" s="24" t="n"/>
+      <c r="AW73" s="24" t="n"/>
+      <c r="AX73" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY73" s="24" t="n"/>
+      <c r="AZ73" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA73" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB73" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC73" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD73" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG73" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH73" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:10.911710Z</t>
+        </is>
+      </c>
+      <c r="BI73" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ73" s="25" t="n"/>
+      <c r="BK73" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL73" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM73" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN73" s="28" t="n"/>
+      <c r="BO73" s="28" t="n"/>
+      <c r="BP73" s="25" t="n"/>
+      <c r="BQ73" s="27" t="n"/>
+      <c r="BR73" s="28" t="n"/>
+      <c r="BS73" s="28" t="n"/>
+      <c r="BT73" s="28" t="n"/>
+      <c r="BU73" s="25" t="n"/>
+      <c r="BV73" s="29" t="n"/>
+      <c r="BW73" s="24" t="n"/>
+      <c r="BX73" s="30" t="n"/>
+      <c r="BY73" s="27" t="n"/>
+      <c r="BZ73" s="24" t="n"/>
+      <c r="CA73" s="31" t="n"/>
+      <c r="CB73" s="24" t="n"/>
+      <c r="CC73" s="24" t="n"/>
+      <c r="CD73" s="24" t="n"/>
+      <c r="CE73" s="24" t="n"/>
+      <c r="CF73" s="24" t="n"/>
+      <c r="CG73" s="24" t="n"/>
+      <c r="CH73" s="24" t="n"/>
+      <c r="CI73" s="24" t="n"/>
+      <c r="CJ73" s="24" t="n"/>
+      <c r="CK73" s="24" t="n"/>
+      <c r="CL73" s="24" t="n"/>
+      <c r="CM73" s="24" t="n"/>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>4af471b2c0fb4a95</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>59852</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>ReThink</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J74" s="25" t="n"/>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M74" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N74" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O74" s="28" t="n">
+        <v>0.71484</v>
+      </c>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="28" t="n">
+        <v>0.124676</v>
+      </c>
+      <c r="R74" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S74" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U74" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V74" s="24" t="n"/>
+      <c r="W74" s="26" t="n"/>
+      <c r="X74" s="26" t="n"/>
+      <c r="Y74" s="25" t="n"/>
+      <c r="Z74" s="26" t="n"/>
+      <c r="AA74" s="28" t="n"/>
+      <c r="AB74" s="28" t="n"/>
+      <c r="AC74" s="30" t="n"/>
+      <c r="AD74" s="24" t="n"/>
+      <c r="AE74" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-sb-rt-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF74" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG74" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH74" s="24" t="n"/>
+      <c r="AI74" s="31" t="n"/>
+      <c r="AJ74" s="31" t="n"/>
+      <c r="AK74" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM74" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN74" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO74" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP74" s="24" t="inlineStr">
+        <is>
+          <t>ReThink</t>
+        </is>
+      </c>
+      <c r="AQ74" s="24" t="inlineStr">
+        <is>
+          <t>ReThink</t>
+        </is>
+      </c>
+      <c r="AR74" s="24" t="inlineStr">
+        <is>
+          <t>ReThink</t>
+        </is>
+      </c>
+      <c r="AS74" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="AT74" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="AU74" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="AV74" s="24" t="n"/>
+      <c r="AW74" s="24" t="n"/>
+      <c r="AX74" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY74" s="24" t="n"/>
+      <c r="AZ74" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA74" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB74" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC74" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD74" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG74" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH74" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:11.725935Z</t>
+        </is>
+      </c>
+      <c r="BI74" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ74" s="25" t="n"/>
+      <c r="BK74" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL74" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM74" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN74" s="28" t="n"/>
+      <c r="BO74" s="28" t="n"/>
+      <c r="BP74" s="25" t="n"/>
+      <c r="BQ74" s="27" t="n"/>
+      <c r="BR74" s="28" t="n"/>
+      <c r="BS74" s="28" t="n"/>
+      <c r="BT74" s="28" t="n"/>
+      <c r="BU74" s="25" t="n"/>
+      <c r="BV74" s="29" t="n"/>
+      <c r="BW74" s="24" t="n"/>
+      <c r="BX74" s="30" t="n"/>
+      <c r="BY74" s="27" t="n"/>
+      <c r="BZ74" s="24" t="n"/>
+      <c r="CA74" s="31" t="n"/>
+      <c r="CB74" s="24" t="n"/>
+      <c r="CC74" s="24" t="n"/>
+      <c r="CD74" s="24" t="n"/>
+      <c r="CE74" s="24" t="n"/>
+      <c r="CF74" s="24" t="n"/>
+      <c r="CG74" s="24" t="n"/>
+      <c r="CH74" s="24" t="n"/>
+      <c r="CI74" s="24" t="n"/>
+      <c r="CJ74" s="24" t="n"/>
+      <c r="CK74" s="24" t="n"/>
+      <c r="CL74" s="24" t="n"/>
+      <c r="CM74" s="24" t="n"/>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>cfdd3bf7f3294d22</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>59851</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>VP.Prodigy</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J75" s="25" t="n"/>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M75" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>0.610402</v>
+      </c>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="28" t="n">
+        <v>0.010402</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S75" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T75" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U75" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="25" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="28" t="n"/>
+      <c r="AB75" s="28" t="n"/>
+      <c r="AC75" s="30" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-bg-vpp-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF75" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG75" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="31" t="n"/>
+      <c r="AK75" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL75" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN75" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO75" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP75" s="24" t="inlineStr">
+        <is>
+          <t>VP.Prodigy</t>
+        </is>
+      </c>
+      <c r="AQ75" s="24" t="inlineStr">
+        <is>
+          <t>VP.Prodigy</t>
+        </is>
+      </c>
+      <c r="AR75" s="24" t="inlineStr">
+        <is>
+          <t>VP.Prodigy</t>
+        </is>
+      </c>
+      <c r="AS75" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="AT75" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="AU75" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA75" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB75" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC75" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD75" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG75" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:12.540718Z</t>
+        </is>
+      </c>
+      <c r="BI75" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ75" s="25" t="n"/>
+      <c r="BK75" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL75" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM75" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN75" s="28" t="n"/>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="25" t="n"/>
+      <c r="BQ75" s="27" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
+      <c r="BT75" s="28" t="n"/>
+      <c r="BU75" s="25" t="n"/>
+      <c r="BV75" s="29" t="n"/>
+      <c r="BW75" s="24" t="n"/>
+      <c r="BX75" s="30" t="n"/>
+      <c r="BY75" s="27" t="n"/>
+      <c r="BZ75" s="24" t="n"/>
+      <c r="CA75" s="31" t="n"/>
+      <c r="CB75" s="24" t="n"/>
+      <c r="CC75" s="24" t="n"/>
+      <c r="CD75" s="24" t="n"/>
+      <c r="CE75" s="24" t="n"/>
+      <c r="CF75" s="24" t="n"/>
+      <c r="CG75" s="24" t="n"/>
+      <c r="CH75" s="24" t="n"/>
+      <c r="CI75" s="24" t="n"/>
+      <c r="CJ75" s="24" t="n"/>
+      <c r="CK75" s="24" t="n"/>
+      <c r="CL75" s="24" t="n"/>
+      <c r="CM75" s="24" t="n"/>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>efb33fe88ad04f1c</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>59848</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>Spirit Academy Green</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Dark Moon</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J76" s="25" t="n"/>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M76" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N76" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O76" s="28" t="n">
+        <v>0.600144</v>
+      </c>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="28" t="n">
+        <v>0.170959</v>
+      </c>
+      <c r="R76" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S76" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T76" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U76" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V76" s="24" t="n"/>
+      <c r="W76" s="26" t="n"/>
+      <c r="X76" s="26" t="n"/>
+      <c r="Y76" s="25" t="n"/>
+      <c r="Z76" s="26" t="n"/>
+      <c r="AA76" s="28" t="n"/>
+      <c r="AB76" s="28" t="n"/>
+      <c r="AC76" s="30" t="n"/>
+      <c r="AD76" s="24" t="n"/>
+      <c r="AE76" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-dm-sag-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF76" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG76" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH76" s="24" t="n"/>
+      <c r="AI76" s="31" t="n"/>
+      <c r="AJ76" s="31" t="n"/>
+      <c r="AK76" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL76" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN76" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO76" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP76" s="24" t="inlineStr">
+        <is>
+          <t>Spirit Academy Green</t>
+        </is>
+      </c>
+      <c r="AQ76" s="24" t="inlineStr">
+        <is>
+          <t>Spirit Academy Green</t>
+        </is>
+      </c>
+      <c r="AR76" s="24" t="inlineStr">
+        <is>
+          <t>Spirit Academy Green</t>
+        </is>
+      </c>
+      <c r="AS76" s="24" t="inlineStr">
+        <is>
+          <t>Dark Moon</t>
+        </is>
+      </c>
+      <c r="AT76" s="24" t="inlineStr">
+        <is>
+          <t>Dark Moon</t>
+        </is>
+      </c>
+      <c r="AU76" s="24" t="inlineStr">
+        <is>
+          <t>Dark Moon</t>
+        </is>
+      </c>
+      <c r="AV76" s="24" t="n"/>
+      <c r="AW76" s="24" t="n"/>
+      <c r="AX76" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY76" s="24" t="n"/>
+      <c r="AZ76" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA76" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB76" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC76" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD76" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE76" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF76" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG76" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH76" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:14.175101Z</t>
+        </is>
+      </c>
+      <c r="BI76" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ76" s="25" t="n"/>
+      <c r="BK76" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL76" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM76" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN76" s="28" t="n"/>
+      <c r="BO76" s="28" t="n"/>
+      <c r="BP76" s="25" t="n"/>
+      <c r="BQ76" s="27" t="n"/>
+      <c r="BR76" s="28" t="n"/>
+      <c r="BS76" s="28" t="n"/>
+      <c r="BT76" s="28" t="n"/>
+      <c r="BU76" s="25" t="n"/>
+      <c r="BV76" s="29" t="n"/>
+      <c r="BW76" s="24" t="n"/>
+      <c r="BX76" s="30" t="n"/>
+      <c r="BY76" s="27" t="n"/>
+      <c r="BZ76" s="24" t="n"/>
+      <c r="CA76" s="31" t="n"/>
+      <c r="CB76" s="24" t="n"/>
+      <c r="CC76" s="24" t="n"/>
+      <c r="CD76" s="24" t="n"/>
+      <c r="CE76" s="24" t="n"/>
+      <c r="CF76" s="24" t="n"/>
+      <c r="CG76" s="24" t="n"/>
+      <c r="CH76" s="24" t="n"/>
+      <c r="CI76" s="24" t="n"/>
+      <c r="CJ76" s="24" t="n"/>
+      <c r="CK76" s="24" t="n"/>
+      <c r="CL76" s="24" t="n"/>
+      <c r="CM76" s="24" t="n"/>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>275051808b7f4b14</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:34.811979Z</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-24T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>59683</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J77" s="25" t="n"/>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M77" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N77" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O77" s="28" t="n">
+        <v>0.627963</v>
+      </c>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="28" t="n">
+        <v>0.118159</v>
+      </c>
+      <c r="R77" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S77" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T77" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U77" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="n"/>
+      <c r="W77" s="26" t="n"/>
+      <c r="X77" s="26" t="n"/>
+      <c r="Y77" s="25" t="n"/>
+      <c r="Z77" s="26" t="n"/>
+      <c r="AA77" s="28" t="n"/>
+      <c r="AB77" s="28" t="n"/>
+      <c r="AC77" s="30" t="n"/>
+      <c r="AD77" s="24" t="n"/>
+      <c r="AE77" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-btf-g2a-2026-07-24).</t>
+        </is>
+      </c>
+      <c r="AF77" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG77" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH77" s="24" t="n"/>
+      <c r="AI77" s="31" t="n"/>
+      <c r="AJ77" s="31" t="n"/>
+      <c r="AK77" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL77" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM77" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN77" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO77" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP77" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AQ77" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AR77" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AS77" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT77" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU77" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV77" s="24" t="n"/>
+      <c r="AW77" s="24" t="n"/>
+      <c r="AX77" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY77" s="24" t="n"/>
+      <c r="AZ77" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA77" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB77" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC77" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD77" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG77" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH77" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:37:30.350274Z</t>
+        </is>
+      </c>
+      <c r="BI77" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ77" s="25" t="n"/>
+      <c r="BK77" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL77" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM77" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN77" s="28" t="n"/>
+      <c r="BO77" s="28" t="n"/>
+      <c r="BP77" s="25" t="n"/>
+      <c r="BQ77" s="27" t="n"/>
+      <c r="BR77" s="28" t="n"/>
+      <c r="BS77" s="28" t="n"/>
+      <c r="BT77" s="28" t="n"/>
+      <c r="BU77" s="25" t="n"/>
+      <c r="BV77" s="29" t="n"/>
+      <c r="BW77" s="24" t="n"/>
+      <c r="BX77" s="30" t="n"/>
+      <c r="BY77" s="27" t="n"/>
+      <c r="BZ77" s="24" t="n"/>
+      <c r="CA77" s="31" t="n"/>
+      <c r="CB77" s="24" t="n"/>
+      <c r="CC77" s="24" t="n"/>
+      <c r="CD77" s="24" t="n"/>
+      <c r="CE77" s="24" t="n"/>
+      <c r="CF77" s="24" t="n"/>
+      <c r="CG77" s="24" t="n"/>
+      <c r="CH77" s="24" t="n"/>
+      <c r="CI77" s="24" t="n"/>
+      <c r="CJ77" s="24" t="n"/>
+      <c r="CK77" s="24" t="n"/>
+      <c r="CL77" s="24" t="n"/>
+      <c r="CM77" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research.xlsx
+++ b/data/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM77" headerRowCount="1">
-  <autoFilter ref="A1:CM77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM79" headerRowCount="1">
+  <autoFilter ref="A1:CM79"/>
   <tableColumns count="91">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -750,19 +750,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$77)</f>
+        <f>COUNTA('Picks'!$A$2:$A$79)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$77,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$79,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$77,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")+COUNTIFS('Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -790,19 +790,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$77,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$79,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")/(COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")+COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")/(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$77)/SUM('Picks'!$BX$2:$BX$77),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$79)/SUM('Picks'!$BX$2:$BX$79),0)</f>
         <v/>
       </c>
     </row>
@@ -830,19 +830,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$77)</f>
+        <f>SUM('Picks'!$BY$2:$BY$79)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$77,"&lt;&gt;",'Picks'!$AB$2:$AB$77),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$79,"&lt;&gt;",'Picks'!$AB$2:$AB$79),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$77,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$77,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$77,'Picks'!$AM$2:$AM$77,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$79,'Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -913,11 +913,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -928,15 +928,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -944,11 +944,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -975,11 +975,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CM77"/>
+  <dimension ref="A1:CM79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21615,6 +21615,524 @@
       <c r="CL77" s="24" t="n"/>
       <c r="CM77" s="24" t="n"/>
     </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>6bcb59f85a5f4db0</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:26:25.160034Z</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>58238</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>Role Swappers</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I78" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J78" s="25" t="n"/>
+      <c r="K78" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L78" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M78" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N78" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O78" s="28" t="n">
+        <v>0.513854</v>
+      </c>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="28" t="n">
+        <v>0.164204</v>
+      </c>
+      <c r="R78" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S78" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T78" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U78" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V78" s="24" t="n"/>
+      <c r="W78" s="26" t="n"/>
+      <c r="X78" s="26" t="n"/>
+      <c r="Y78" s="25" t="n"/>
+      <c r="Z78" s="26" t="n"/>
+      <c r="AA78" s="28" t="n"/>
+      <c r="AB78" s="28" t="n"/>
+      <c r="AC78" s="30" t="n"/>
+      <c r="AD78" s="24" t="n"/>
+      <c r="AE78" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-lol-role-wd-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF78" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG78" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH78" s="24" t="n"/>
+      <c r="AI78" s="31" t="n"/>
+      <c r="AJ78" s="31" t="n"/>
+      <c r="AK78" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL78" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM78" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN78" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO78" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP78" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="AQ78" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="AR78" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="AS78" s="24" t="inlineStr">
+        <is>
+          <t>Role Swappers</t>
+        </is>
+      </c>
+      <c r="AT78" s="24" t="inlineStr">
+        <is>
+          <t>Role Swappers</t>
+        </is>
+      </c>
+      <c r="AU78" s="24" t="inlineStr">
+        <is>
+          <t>Role Swappers</t>
+        </is>
+      </c>
+      <c r="AV78" s="24" t="n"/>
+      <c r="AW78" s="24" t="n"/>
+      <c r="AX78" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY78" s="24" t="n"/>
+      <c r="AZ78" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA78" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BB78" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC78" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD78" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BE78" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF78" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG78" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH78" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:26:14.981806Z</t>
+        </is>
+      </c>
+      <c r="BI78" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ78" s="25" t="n"/>
+      <c r="BK78" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL78" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM78" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN78" s="28" t="n"/>
+      <c r="BO78" s="28" t="n"/>
+      <c r="BP78" s="25" t="n"/>
+      <c r="BQ78" s="27" t="n"/>
+      <c r="BR78" s="28" t="n"/>
+      <c r="BS78" s="28" t="n"/>
+      <c r="BT78" s="28" t="n"/>
+      <c r="BU78" s="25" t="n"/>
+      <c r="BV78" s="29" t="n"/>
+      <c r="BW78" s="24" t="n"/>
+      <c r="BX78" s="30" t="n"/>
+      <c r="BY78" s="27" t="n"/>
+      <c r="BZ78" s="24" t="n"/>
+      <c r="CA78" s="31" t="n"/>
+      <c r="CB78" s="24" t="n"/>
+      <c r="CC78" s="24" t="n"/>
+      <c r="CD78" s="24" t="n"/>
+      <c r="CE78" s="24" t="n"/>
+      <c r="CF78" s="24" t="n"/>
+      <c r="CG78" s="24" t="n"/>
+      <c r="CH78" s="24" t="n"/>
+      <c r="CI78" s="24" t="n"/>
+      <c r="CJ78" s="24" t="n"/>
+      <c r="CK78" s="24" t="n"/>
+      <c r="CL78" s="24" t="n"/>
+      <c r="CM78" s="24" t="n"/>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>90b3d877e20d4290</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:27:00.632921Z</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>59850</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J79" s="25" t="n"/>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M79" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N79" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O79" s="28" t="n">
+        <v>0.504359</v>
+      </c>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="28" t="n">
+        <v>0.034875</v>
+      </c>
+      <c r="R79" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S79" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T79" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U79" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V79" s="24" t="n"/>
+      <c r="W79" s="26" t="n"/>
+      <c r="X79" s="26" t="n"/>
+      <c r="Y79" s="25" t="n"/>
+      <c r="Z79" s="26" t="n"/>
+      <c r="AA79" s="28" t="n"/>
+      <c r="AB79" s="28" t="n"/>
+      <c r="AC79" s="30" t="n"/>
+      <c r="AD79" s="24" t="n"/>
+      <c r="AE79" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-enr-nve-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF79" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG79" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH79" s="24" t="n"/>
+      <c r="AI79" s="31" t="n"/>
+      <c r="AJ79" s="31" t="n"/>
+      <c r="AK79" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL79" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM79" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN79" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO79" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP79" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="AQ79" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="AR79" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="AS79" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AT79" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AU79" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AV79" s="24" t="n"/>
+      <c r="AW79" s="24" t="n"/>
+      <c r="AX79" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY79" s="24" t="n"/>
+      <c r="AZ79" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA79" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB79" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC79" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD79" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG79" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH79" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:26:40.388327Z</t>
+        </is>
+      </c>
+      <c r="BI79" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ79" s="25" t="n"/>
+      <c r="BK79" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL79" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM79" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN79" s="28" t="n"/>
+      <c r="BO79" s="28" t="n"/>
+      <c r="BP79" s="25" t="n"/>
+      <c r="BQ79" s="27" t="n"/>
+      <c r="BR79" s="28" t="n"/>
+      <c r="BS79" s="28" t="n"/>
+      <c r="BT79" s="28" t="n"/>
+      <c r="BU79" s="25" t="n"/>
+      <c r="BV79" s="29" t="n"/>
+      <c r="BW79" s="24" t="n"/>
+      <c r="BX79" s="30" t="n"/>
+      <c r="BY79" s="27" t="n"/>
+      <c r="BZ79" s="24" t="n"/>
+      <c r="CA79" s="31" t="n"/>
+      <c r="CB79" s="24" t="n"/>
+      <c r="CC79" s="24" t="n"/>
+      <c r="CD79" s="24" t="n"/>
+      <c r="CE79" s="24" t="n"/>
+      <c r="CF79" s="24" t="n"/>
+      <c r="CG79" s="24" t="n"/>
+      <c r="CH79" s="24" t="n"/>
+      <c r="CI79" s="24" t="n"/>
+      <c r="CJ79" s="24" t="n"/>
+      <c r="CK79" s="24" t="n"/>
+      <c r="CL79" s="24" t="n"/>
+      <c r="CM79" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research.xlsx
+++ b/data/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM79" headerRowCount="1">
-  <autoFilter ref="A1:CM79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM85" headerRowCount="1">
+  <autoFilter ref="A1:CM85"/>
   <tableColumns count="91">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -750,19 +750,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$79)</f>
+        <f>COUNTA('Picks'!$A$2:$A$85)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$79,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$85,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")+COUNTIFS('Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -790,19 +790,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$79,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$85,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")/(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"win")/(COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"win")+COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$79)/SUM('Picks'!$BX$2:$BX$79),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$85)/SUM('Picks'!$BX$2:$BX$85),0)</f>
         <v/>
       </c>
     </row>
@@ -830,19 +830,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$79)</f>
+        <f>SUM('Picks'!$BY$2:$BY$85)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$79,"&lt;&gt;",'Picks'!$AB$2:$AB$79),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$85,"&lt;&gt;",'Picks'!$AB$2:$AB$85),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$85,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$79,'Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$85,'Picks'!$AM$2:$AM$85,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -913,11 +913,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$85,'Picks'!$H$2:$H$85,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$85,'Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -928,15 +928,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -944,11 +944,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$85,'Picks'!$H$2:$H$85,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$85,'Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -975,11 +975,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$85,'Picks'!$H$2:$H$85,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$85,'Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CM79"/>
+  <dimension ref="A1:CM85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3527,18 +3527,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:34:29.539199Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-100t-ntr-2026-07-23).</t>
@@ -12788,18 +12802,32 @@
       </c>
       <c r="U44" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y44" s="25" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
+      <c r="AC44" s="30" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AD44" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:34:40.105334Z</t>
+        </is>
+      </c>
       <c r="AE44" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-100t-ntr-2026-07-23).</t>
@@ -22133,6 +22161,1560 @@
       <c r="CL79" s="24" t="n"/>
       <c r="CM79" s="24" t="n"/>
     </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>2d3f5fba93944fa5</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:35:50.881798Z</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>58235</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>EXSAD Gaming</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J80" s="25" t="n"/>
+      <c r="K80" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M80" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N80" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O80" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="28" t="n">
+        <v>-0.15035</v>
+      </c>
+      <c r="R80" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T80" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U80" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V80" s="24" t="n"/>
+      <c r="W80" s="26" t="n"/>
+      <c r="X80" s="26" t="n"/>
+      <c r="Y80" s="25" t="n"/>
+      <c r="Z80" s="26" t="n"/>
+      <c r="AA80" s="28" t="n"/>
+      <c r="AB80" s="28" t="n"/>
+      <c r="AC80" s="30" t="n"/>
+      <c r="AD80" s="24" t="n"/>
+      <c r="AE80" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-capy-exg-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF80" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG80" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH80" s="24" t="n"/>
+      <c r="AI80" s="31" t="n"/>
+      <c r="AJ80" s="31" t="n"/>
+      <c r="AK80" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL80" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM80" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN80" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO80" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP80" s="24" t="inlineStr">
+        <is>
+          <t>EXSAD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ80" s="24" t="inlineStr">
+        <is>
+          <t>EXSAD Gaming</t>
+        </is>
+      </c>
+      <c r="AR80" s="24" t="inlineStr">
+        <is>
+          <t>EXSAD Gaming</t>
+        </is>
+      </c>
+      <c r="AS80" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AT80" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AU80" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AV80" s="24" t="n"/>
+      <c r="AW80" s="24" t="n"/>
+      <c r="AX80" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY80" s="24" t="n"/>
+      <c r="AZ80" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA80" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BB80" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC80" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD80" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BE80" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF80" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG80" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH80" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:35:35.265338Z</t>
+        </is>
+      </c>
+      <c r="BI80" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ80" s="25" t="n"/>
+      <c r="BK80" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL80" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM80" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN80" s="28" t="n"/>
+      <c r="BO80" s="28" t="n"/>
+      <c r="BP80" s="25" t="n"/>
+      <c r="BQ80" s="27" t="n"/>
+      <c r="BR80" s="28" t="n"/>
+      <c r="BS80" s="28" t="n"/>
+      <c r="BT80" s="28" t="n"/>
+      <c r="BU80" s="25" t="n"/>
+      <c r="BV80" s="29" t="n"/>
+      <c r="BW80" s="24" t="n"/>
+      <c r="BX80" s="30" t="n"/>
+      <c r="BY80" s="27" t="n"/>
+      <c r="BZ80" s="24" t="n"/>
+      <c r="CA80" s="31" t="n"/>
+      <c r="CB80" s="24" t="n"/>
+      <c r="CC80" s="24" t="n"/>
+      <c r="CD80" s="24" t="n"/>
+      <c r="CE80" s="24" t="n"/>
+      <c r="CF80" s="24" t="n"/>
+      <c r="CG80" s="24" t="n"/>
+      <c r="CH80" s="24" t="n"/>
+      <c r="CI80" s="24" t="n"/>
+      <c r="CJ80" s="24" t="n"/>
+      <c r="CK80" s="24" t="n"/>
+      <c r="CL80" s="24" t="n"/>
+      <c r="CM80" s="24" t="n"/>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>fbfa8685a306416e</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:35:50.881798Z</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-24T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>58454</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J81" s="25" t="n"/>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M81" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N81" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O81" s="28" t="n">
+        <v>0.5851769999999999</v>
+      </c>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="28" t="n">
+        <v>0.155992</v>
+      </c>
+      <c r="R81" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S81" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T81" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U81" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V81" s="24" t="n"/>
+      <c r="W81" s="26" t="n"/>
+      <c r="X81" s="26" t="n"/>
+      <c r="Y81" s="25" t="n"/>
+      <c r="Z81" s="26" t="n"/>
+      <c r="AA81" s="28" t="n"/>
+      <c r="AB81" s="28" t="n"/>
+      <c r="AC81" s="30" t="n"/>
+      <c r="AD81" s="24" t="n"/>
+      <c r="AE81" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-p11-gmb-2026-07-24).</t>
+        </is>
+      </c>
+      <c r="AF81" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG81" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH81" s="24" t="n"/>
+      <c r="AI81" s="31" t="n"/>
+      <c r="AJ81" s="31" t="n"/>
+      <c r="AK81" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL81" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM81" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN81" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO81" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP81" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AQ81" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AR81" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AS81" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AT81" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AU81" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AV81" s="24" t="n"/>
+      <c r="AW81" s="24" t="n"/>
+      <c r="AX81" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY81" s="24" t="n"/>
+      <c r="AZ81" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA81" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BB81" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC81" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD81" s="24" t="inlineStr">
+        <is>
+          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
+        </is>
+      </c>
+      <c r="BE81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG81" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH81" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:35:47.586016Z</t>
+        </is>
+      </c>
+      <c r="BI81" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ81" s="25" t="n"/>
+      <c r="BK81" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL81" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM81" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN81" s="28" t="n"/>
+      <c r="BO81" s="28" t="n"/>
+      <c r="BP81" s="25" t="n"/>
+      <c r="BQ81" s="27" t="n"/>
+      <c r="BR81" s="28" t="n"/>
+      <c r="BS81" s="28" t="n"/>
+      <c r="BT81" s="28" t="n"/>
+      <c r="BU81" s="25" t="n"/>
+      <c r="BV81" s="29" t="n"/>
+      <c r="BW81" s="24" t="n"/>
+      <c r="BX81" s="30" t="n"/>
+      <c r="BY81" s="27" t="n"/>
+      <c r="BZ81" s="24" t="n"/>
+      <c r="CA81" s="31" t="n"/>
+      <c r="CB81" s="24" t="n"/>
+      <c r="CC81" s="24" t="n"/>
+      <c r="CD81" s="24" t="n"/>
+      <c r="CE81" s="24" t="n"/>
+      <c r="CF81" s="24" t="n"/>
+      <c r="CG81" s="24" t="n"/>
+      <c r="CH81" s="24" t="n"/>
+      <c r="CI81" s="24" t="n"/>
+      <c r="CJ81" s="24" t="n"/>
+      <c r="CK81" s="24" t="n"/>
+      <c r="CL81" s="24" t="n"/>
+      <c r="CM81" s="24" t="n"/>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>b948ea8c0be54c58</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:27.605488Z</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-24T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>Walczaki</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J82" s="25" t="n"/>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M82" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N82" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O82" s="28" t="n">
+        <v>0.517334</v>
+      </c>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="28" t="n">
+        <v>-0.152633</v>
+      </c>
+      <c r="R82" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T82" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U82" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V82" s="24" t="n"/>
+      <c r="W82" s="26" t="n"/>
+      <c r="X82" s="26" t="n"/>
+      <c r="Y82" s="25" t="n"/>
+      <c r="Z82" s="26" t="n"/>
+      <c r="AA82" s="28" t="n"/>
+      <c r="AB82" s="28" t="n"/>
+      <c r="AC82" s="30" t="n"/>
+      <c r="AD82" s="24" t="n"/>
+      <c r="AE82" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-m8-wal-2026-07-24).</t>
+        </is>
+      </c>
+      <c r="AF82" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG82" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH82" s="24" t="n"/>
+      <c r="AI82" s="31" t="n"/>
+      <c r="AJ82" s="31" t="n"/>
+      <c r="AK82" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL82" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM82" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP82" s="24" t="inlineStr">
+        <is>
+          <t>Walczaki</t>
+        </is>
+      </c>
+      <c r="AQ82" s="24" t="inlineStr">
+        <is>
+          <t>Walczaki</t>
+        </is>
+      </c>
+      <c r="AR82" s="24" t="inlineStr">
+        <is>
+          <t>Walczaki</t>
+        </is>
+      </c>
+      <c r="AS82" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AT82" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AU82" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AV82" s="24" t="n"/>
+      <c r="AW82" s="24" t="n"/>
+      <c r="AX82" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY82" s="24" t="n"/>
+      <c r="AZ82" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA82" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB82" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC82" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD82" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG82" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:22.454543Z</t>
+        </is>
+      </c>
+      <c r="BI82" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ82" s="25" t="n"/>
+      <c r="BK82" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL82" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM82" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN82" s="28" t="n"/>
+      <c r="BO82" s="28" t="n"/>
+      <c r="BP82" s="25" t="n"/>
+      <c r="BQ82" s="27" t="n"/>
+      <c r="BR82" s="28" t="n"/>
+      <c r="BS82" s="28" t="n"/>
+      <c r="BT82" s="28" t="n"/>
+      <c r="BU82" s="25" t="n"/>
+      <c r="BV82" s="29" t="n"/>
+      <c r="BW82" s="24" t="n"/>
+      <c r="BX82" s="30" t="n"/>
+      <c r="BY82" s="27" t="n"/>
+      <c r="BZ82" s="24" t="n"/>
+      <c r="CA82" s="31" t="n"/>
+      <c r="CB82" s="24" t="n"/>
+      <c r="CC82" s="24" t="n"/>
+      <c r="CD82" s="24" t="n"/>
+      <c r="CE82" s="24" t="n"/>
+      <c r="CF82" s="24" t="n"/>
+      <c r="CG82" s="24" t="n"/>
+      <c r="CH82" s="24" t="n"/>
+      <c r="CI82" s="24" t="n"/>
+      <c r="CJ82" s="24" t="n"/>
+      <c r="CK82" s="24" t="n"/>
+      <c r="CL82" s="24" t="n"/>
+      <c r="CM82" s="24" t="n"/>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>ec5f8d7b7b024e96</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:27.605488Z</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-24T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>59043</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J83" s="25" t="n"/>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M83" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N83" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O83" s="28" t="n">
+        <v>0.5724050000000001</v>
+      </c>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="28" t="n">
+        <v>-0.097562</v>
+      </c>
+      <c r="R83" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T83" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U83" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="n"/>
+      <c r="W83" s="26" t="n"/>
+      <c r="X83" s="26" t="n"/>
+      <c r="Y83" s="25" t="n"/>
+      <c r="Z83" s="26" t="n"/>
+      <c r="AA83" s="28" t="n"/>
+      <c r="AB83" s="28" t="n"/>
+      <c r="AC83" s="30" t="n"/>
+      <c r="AD83" s="24" t="n"/>
+      <c r="AE83" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-g1-atr-2026-07-24).</t>
+        </is>
+      </c>
+      <c r="AF83" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG83" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH83" s="24" t="n"/>
+      <c r="AI83" s="31" t="n"/>
+      <c r="AJ83" s="31" t="n"/>
+      <c r="AK83" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL83" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM83" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP83" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="AQ83" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="AR83" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="AS83" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="AT83" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="AU83" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="AV83" s="24" t="n"/>
+      <c r="AW83" s="24" t="n"/>
+      <c r="AX83" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY83" s="24" t="n"/>
+      <c r="AZ83" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA83" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB83" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC83" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD83" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG83" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:23.372169Z</t>
+        </is>
+      </c>
+      <c r="BI83" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ83" s="25" t="n"/>
+      <c r="BK83" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL83" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM83" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN83" s="28" t="n"/>
+      <c r="BO83" s="28" t="n"/>
+      <c r="BP83" s="25" t="n"/>
+      <c r="BQ83" s="27" t="n"/>
+      <c r="BR83" s="28" t="n"/>
+      <c r="BS83" s="28" t="n"/>
+      <c r="BT83" s="28" t="n"/>
+      <c r="BU83" s="25" t="n"/>
+      <c r="BV83" s="29" t="n"/>
+      <c r="BW83" s="24" t="n"/>
+      <c r="BX83" s="30" t="n"/>
+      <c r="BY83" s="27" t="n"/>
+      <c r="BZ83" s="24" t="n"/>
+      <c r="CA83" s="31" t="n"/>
+      <c r="CB83" s="24" t="n"/>
+      <c r="CC83" s="24" t="n"/>
+      <c r="CD83" s="24" t="n"/>
+      <c r="CE83" s="24" t="n"/>
+      <c r="CF83" s="24" t="n"/>
+      <c r="CG83" s="24" t="n"/>
+      <c r="CH83" s="24" t="n"/>
+      <c r="CI83" s="24" t="n"/>
+      <c r="CJ83" s="24" t="n"/>
+      <c r="CK83" s="24" t="n"/>
+      <c r="CL83" s="24" t="n"/>
+      <c r="CM83" s="24" t="n"/>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>0290b65f79474bcb</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:27.605488Z</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-24T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>59967</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>Keyd</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J84" s="25" t="n"/>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M84" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N84" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O84" s="28" t="n">
+        <v>0.568001</v>
+      </c>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="28" t="n">
+        <v>-0.041374</v>
+      </c>
+      <c r="R84" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T84" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U84" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="n"/>
+      <c r="W84" s="26" t="n"/>
+      <c r="X84" s="26" t="n"/>
+      <c r="Y84" s="25" t="n"/>
+      <c r="Z84" s="26" t="n"/>
+      <c r="AA84" s="28" t="n"/>
+      <c r="AB84" s="28" t="n"/>
+      <c r="AC84" s="30" t="n"/>
+      <c r="AD84" s="24" t="n"/>
+      <c r="AE84" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-keyd-alka-2026-07-24).</t>
+        </is>
+      </c>
+      <c r="AF84" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG84" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH84" s="24" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="31" t="n"/>
+      <c r="AK84" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL84" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM84" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP84" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AQ84" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AR84" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AS84" s="24" t="inlineStr">
+        <is>
+          <t>Keyd</t>
+        </is>
+      </c>
+      <c r="AT84" s="24" t="inlineStr">
+        <is>
+          <t>Keyd</t>
+        </is>
+      </c>
+      <c r="AU84" s="24" t="inlineStr">
+        <is>
+          <t>Keyd</t>
+        </is>
+      </c>
+      <c r="AV84" s="24" t="n"/>
+      <c r="AW84" s="24" t="n"/>
+      <c r="AX84" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY84" s="24" t="n"/>
+      <c r="AZ84" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA84" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BB84" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC84" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD84" s="24" t="inlineStr">
+        <is>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
+        </is>
+      </c>
+      <c r="BE84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG84" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:26.758550Z</t>
+        </is>
+      </c>
+      <c r="BI84" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ84" s="25" t="n"/>
+      <c r="BK84" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL84" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM84" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN84" s="28" t="n"/>
+      <c r="BO84" s="28" t="n"/>
+      <c r="BP84" s="25" t="n"/>
+      <c r="BQ84" s="27" t="n"/>
+      <c r="BR84" s="28" t="n"/>
+      <c r="BS84" s="28" t="n"/>
+      <c r="BT84" s="28" t="n"/>
+      <c r="BU84" s="25" t="n"/>
+      <c r="BV84" s="29" t="n"/>
+      <c r="BW84" s="24" t="n"/>
+      <c r="BX84" s="30" t="n"/>
+      <c r="BY84" s="27" t="n"/>
+      <c r="BZ84" s="24" t="n"/>
+      <c r="CA84" s="31" t="n"/>
+      <c r="CB84" s="24" t="n"/>
+      <c r="CC84" s="24" t="n"/>
+      <c r="CD84" s="24" t="n"/>
+      <c r="CE84" s="24" t="n"/>
+      <c r="CF84" s="24" t="n"/>
+      <c r="CG84" s="24" t="n"/>
+      <c r="CH84" s="24" t="n"/>
+      <c r="CI84" s="24" t="n"/>
+      <c r="CJ84" s="24" t="n"/>
+      <c r="CK84" s="24" t="n"/>
+      <c r="CL84" s="24" t="n"/>
+      <c r="CM84" s="24" t="n"/>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>97a20129d01c4f3a</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:54.423225Z</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>57152</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J85" s="25" t="n"/>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M85" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N85" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O85" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="28" t="n">
+        <v>-0.119772</v>
+      </c>
+      <c r="R85" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T85" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U85" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V85" s="24" t="n"/>
+      <c r="W85" s="26" t="n"/>
+      <c r="X85" s="26" t="n"/>
+      <c r="Y85" s="25" t="n"/>
+      <c r="Z85" s="26" t="n"/>
+      <c r="AA85" s="28" t="n"/>
+      <c r="AB85" s="28" t="n"/>
+      <c r="AC85" s="30" t="n"/>
+      <c r="AD85" s="24" t="n"/>
+      <c r="AE85" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-kcg-aar-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF85" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG85" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH85" s="24" t="n"/>
+      <c r="AI85" s="31" t="n"/>
+      <c r="AJ85" s="31" t="n"/>
+      <c r="AK85" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL85" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM85" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP85" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AQ85" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AR85" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AS85" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AT85" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AU85" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AV85" s="24" t="n"/>
+      <c r="AW85" s="24" t="n"/>
+      <c r="AX85" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY85" s="24" t="n"/>
+      <c r="AZ85" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA85" s="24" t="inlineStr">
+        <is>
+          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
+        </is>
+      </c>
+      <c r="BB85" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC85" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD85" s="24" t="inlineStr">
+        <is>
+          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
+        </is>
+      </c>
+      <c r="BE85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG85" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:36:43.922293Z</t>
+        </is>
+      </c>
+      <c r="BI85" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ85" s="25" t="n"/>
+      <c r="BK85" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL85" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM85" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN85" s="28" t="n"/>
+      <c r="BO85" s="28" t="n"/>
+      <c r="BP85" s="25" t="n"/>
+      <c r="BQ85" s="27" t="n"/>
+      <c r="BR85" s="28" t="n"/>
+      <c r="BS85" s="28" t="n"/>
+      <c r="BT85" s="28" t="n"/>
+      <c r="BU85" s="25" t="n"/>
+      <c r="BV85" s="29" t="n"/>
+      <c r="BW85" s="24" t="n"/>
+      <c r="BX85" s="30" t="n"/>
+      <c r="BY85" s="27" t="n"/>
+      <c r="BZ85" s="24" t="n"/>
+      <c r="CA85" s="31" t="n"/>
+      <c r="CB85" s="24" t="n"/>
+      <c r="CC85" s="24" t="n"/>
+      <c r="CD85" s="24" t="n"/>
+      <c r="CE85" s="24" t="n"/>
+      <c r="CF85" s="24" t="n"/>
+      <c r="CG85" s="24" t="n"/>
+      <c r="CH85" s="24" t="n"/>
+      <c r="CI85" s="24" t="n"/>
+      <c r="CJ85" s="24" t="n"/>
+      <c r="CK85" s="24" t="n"/>
+      <c r="CL85" s="24" t="n"/>
+      <c r="CM85" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research.xlsx
+++ b/data/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO136" headerRowCount="1">
-  <autoFilter ref="A1:CO136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO139" headerRowCount="1">
+  <autoFilter ref="A1:CO139"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$136)</f>
+        <f>COUNTA('Picks'!$A$2:$A$139)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$136,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$139,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")+COUNTIFS('Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")+COUNTIFS('Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$136,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$139,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"win")/(COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"win")+COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"win")/(COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"win")+COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$136)/SUM('Picks'!$BX$2:$BX$136),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$139)/SUM('Picks'!$BX$2:$BX$139),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$136)</f>
+        <f>SUM('Picks'!$BY$2:$BY$139)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$136,"&lt;&gt;",'Picks'!$AB$2:$AB$136),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$139,"&lt;&gt;",'Picks'!$AB$2:$AB$139),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$136,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$139,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$136,'Picks'!$AM$2:$AM$136,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$139,'Picks'!$AM$2:$AM$139,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$136,'Picks'!$H$2:$H$136,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$139,'Picks'!$H$2:$H$139,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$136,'Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$139,'Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$136,'Picks'!$H$2:$H$136,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$139,'Picks'!$H$2:$H$139,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$136,'Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$139,'Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$136,'Picks'!$H$2:$H$136,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$139,'Picks'!$H$2:$H$139,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$136,'Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$139,'Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO136"/>
+  <dimension ref="A1:CO139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25354,18 +25354,32 @@
       </c>
       <c r="U88" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V88" s="24" t="n"/>
-      <c r="W88" s="26" t="n"/>
-      <c r="X88" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V88" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W88" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X88" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y88" s="25" t="n"/>
       <c r="Z88" s="26" t="n"/>
       <c r="AA88" s="28" t="n"/>
       <c r="AB88" s="28" t="n"/>
-      <c r="AC88" s="30" t="n"/>
-      <c r="AD88" s="24" t="n"/>
+      <c r="AC88" s="30" t="n">
+        <v>1.3333</v>
+      </c>
+      <c r="AD88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:18.709773Z</t>
+        </is>
+      </c>
       <c r="AE88" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-al-blg-2026-07-26).</t>
@@ -25615,18 +25629,32 @@
       </c>
       <c r="U89" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V89" s="24" t="n"/>
-      <c r="W89" s="26" t="n"/>
-      <c r="X89" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V89" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y89" s="25" t="n"/>
       <c r="Z89" s="26" t="n"/>
       <c r="AA89" s="28" t="n"/>
       <c r="AB89" s="28" t="n"/>
-      <c r="AC89" s="30" t="n"/>
-      <c r="AD89" s="24" t="n"/>
+      <c r="AC89" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:20.620042Z</t>
+        </is>
+      </c>
       <c r="AE89" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-cfo-dcg-2026-07-26).</t>
@@ -25639,7 +25667,7 @@
       </c>
       <c r="AG89" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH89" s="24" t="n"/>
@@ -26151,18 +26179,32 @@
       </c>
       <c r="U91" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V91" s="24" t="n"/>
-      <c r="W91" s="26" t="n"/>
-      <c r="X91" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V91" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W91" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X91" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y91" s="25" t="n"/>
       <c r="Z91" s="26" t="n"/>
       <c r="AA91" s="28" t="n"/>
       <c r="AB91" s="28" t="n"/>
-      <c r="AC91" s="30" t="n"/>
-      <c r="AD91" s="24" t="n"/>
+      <c r="AC91" s="30" t="n">
+        <v>1.5487</v>
+      </c>
+      <c r="AD91" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:22.477994Z</t>
+        </is>
+      </c>
       <c r="AE91" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-nve-exmana-2026-07-26).</t>
@@ -26412,18 +26454,32 @@
       </c>
       <c r="U92" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V92" s="24" t="n"/>
-      <c r="W92" s="26" t="n"/>
-      <c r="X92" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V92" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y92" s="25" t="n"/>
       <c r="Z92" s="26" t="n"/>
       <c r="AA92" s="28" t="n"/>
       <c r="AB92" s="28" t="n"/>
-      <c r="AC92" s="30" t="n"/>
-      <c r="AD92" s="24" t="n"/>
+      <c r="AC92" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD92" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:24.261709Z</t>
+        </is>
+      </c>
       <c r="AE92" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-btf-sawy-2026-07-26).</t>
@@ -26436,7 +26492,7 @@
       </c>
       <c r="AG92" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH92" s="24" t="n"/>
@@ -26673,18 +26729,32 @@
       </c>
       <c r="U93" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V93" s="24" t="n"/>
-      <c r="W93" s="26" t="n"/>
-      <c r="X93" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V93" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W93" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y93" s="25" t="n"/>
       <c r="Z93" s="26" t="n"/>
       <c r="AA93" s="28" t="n"/>
       <c r="AB93" s="28" t="n"/>
-      <c r="AC93" s="30" t="n"/>
-      <c r="AD93" s="24" t="n"/>
+      <c r="AC93" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD93" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:26.193815Z</t>
+        </is>
+      </c>
       <c r="AE93" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-inox-pha-2026-07-26).</t>
@@ -26697,7 +26767,7 @@
       </c>
       <c r="AG93" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH93" s="24" t="n"/>
@@ -26934,18 +27004,32 @@
       </c>
       <c r="U94" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V94" s="24" t="n"/>
-      <c r="W94" s="26" t="n"/>
-      <c r="X94" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V94" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W94" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X94" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y94" s="25" t="n"/>
       <c r="Z94" s="26" t="n"/>
       <c r="AA94" s="28" t="n"/>
       <c r="AB94" s="28" t="n"/>
-      <c r="AC94" s="30" t="n"/>
-      <c r="AD94" s="24" t="n"/>
+      <c r="AC94" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD94" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:28.050577Z</t>
+        </is>
+      </c>
       <c r="AE94" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-misa-mta-2026-07-26).</t>
@@ -26958,7 +27042,7 @@
       </c>
       <c r="AG94" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH94" s="24" t="n"/>
@@ -27195,18 +27279,32 @@
       </c>
       <c r="U95" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V95" s="24" t="n"/>
-      <c r="W95" s="26" t="n"/>
-      <c r="X95" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V95" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W95" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y95" s="25" t="n"/>
       <c r="Z95" s="26" t="n"/>
       <c r="AA95" s="28" t="n"/>
       <c r="AB95" s="28" t="n"/>
-      <c r="AC95" s="30" t="n"/>
-      <c r="AD95" s="24" t="n"/>
+      <c r="AC95" s="30" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="AD95" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:29.943635Z</t>
+        </is>
+      </c>
       <c r="AE95" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-ill-nemiga-2026-07-26).</t>
@@ -27731,18 +27829,32 @@
       </c>
       <c r="U97" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V97" s="24" t="n"/>
-      <c r="W97" s="26" t="n"/>
-      <c r="X97" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V97" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W97" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y97" s="25" t="n"/>
       <c r="Z97" s="26" t="n"/>
       <c r="AA97" s="28" t="n"/>
       <c r="AB97" s="28" t="n"/>
-      <c r="AC97" s="30" t="n"/>
-      <c r="AD97" s="24" t="n"/>
+      <c r="AC97" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD97" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:32.016825Z</t>
+        </is>
+      </c>
       <c r="AE97" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-nova-blg-2026-07-26).</t>
@@ -27992,18 +28104,32 @@
       </c>
       <c r="U98" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V98" s="24" t="n"/>
-      <c r="W98" s="26" t="n"/>
-      <c r="X98" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V98" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W98" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y98" s="25" t="n"/>
       <c r="Z98" s="26" t="n"/>
       <c r="AA98" s="28" t="n"/>
       <c r="AB98" s="28" t="n"/>
-      <c r="AC98" s="30" t="n"/>
-      <c r="AD98" s="24" t="n"/>
+      <c r="AC98" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD98" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:33.905977Z</t>
+        </is>
+      </c>
       <c r="AE98" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-gls-thg-2026-07-26).</t>
@@ -28016,7 +28142,7 @@
       </c>
       <c r="AG98" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH98" s="24" t="n"/>
@@ -28253,18 +28379,32 @@
       </c>
       <c r="U99" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V99" s="24" t="n"/>
-      <c r="W99" s="26" t="n"/>
-      <c r="X99" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V99" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W99" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X99" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y99" s="25" t="n"/>
       <c r="Z99" s="26" t="n"/>
       <c r="AA99" s="28" t="n"/>
       <c r="AB99" s="28" t="n"/>
-      <c r="AC99" s="30" t="n"/>
-      <c r="AD99" s="24" t="n"/>
+      <c r="AC99" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD99" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:35.819648Z</t>
+        </is>
+      </c>
       <c r="AE99" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-lil-cla-2026-07-26).</t>
@@ -28277,7 +28417,7 @@
       </c>
       <c r="AG99" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH99" s="24" t="n"/>
@@ -28697,37 +28837,37 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>0219d015362d4091</t>
+          <t>86195cd6ef414a9d</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:00Z</t>
+          <t>2026-07-26T14:00:00Z</t>
         </is>
       </c>
       <c r="D101" s="24" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>61030</t>
         </is>
       </c>
       <c r="E101" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr">
@@ -28747,49 +28887,63 @@
         </is>
       </c>
       <c r="L101" s="26" t="n">
-        <v>-138</v>
+        <v>-233</v>
       </c>
       <c r="M101" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.429185</v>
       </c>
       <c r="N101" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6997</v>
       </c>
       <c r="O101" s="28" t="n">
-        <v>0.723066</v>
+        <v>0.603297</v>
       </c>
       <c r="P101" s="28" t="n"/>
       <c r="Q101" s="28" t="n">
-        <v>0.143234</v>
+        <v>-0.096403</v>
       </c>
       <c r="R101" s="26" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="S101" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T101" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U101" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V101" s="24" t="n"/>
-      <c r="W101" s="26" t="n"/>
-      <c r="X101" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V101" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y101" s="25" t="n"/>
       <c r="Z101" s="26" t="n"/>
       <c r="AA101" s="28" t="n"/>
       <c r="AB101" s="28" t="n"/>
-      <c r="AC101" s="30" t="n"/>
-      <c r="AD101" s="24" t="n"/>
+      <c r="AC101" s="30" t="n">
+        <v>0.6438</v>
+      </c>
+      <c r="AD101" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:25:22.025515Z</t>
+        </is>
+      </c>
       <c r="AE101" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-tl-c9-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-inox-g2a-2026-07-26).</t>
         </is>
       </c>
       <c r="AF101" s="31" t="inlineStr">
@@ -28830,32 +28984,32 @@
       </c>
       <c r="AP101" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AQ101" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AR101" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AS101" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="AT101" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="AU101" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="AV101" s="24" t="n"/>
@@ -28873,7 +29027,7 @@
       </c>
       <c r="BA101" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB101" s="24" t="inlineStr">
@@ -28883,12 +29037,12 @@
       </c>
       <c r="BC101" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD101" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE101" s="24" t="inlineStr">
@@ -28903,12 +29057,12 @@
       </c>
       <c r="BG101" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:14.812794Z</t>
+          <t>2026-07-26T12:49:42.821812Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -28918,13 +29072,13 @@
       </c>
       <c r="BJ101" s="25" t="n"/>
       <c r="BK101" s="26" t="n">
-        <v>-138</v>
+        <v>-233</v>
       </c>
       <c r="BL101" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.429185</v>
       </c>
       <c r="BM101" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6997</v>
       </c>
       <c r="BN101" s="28" t="n"/>
       <c r="BO101" s="28" t="n"/>
@@ -28958,37 +29112,37 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>5d4d4a253098425a</t>
+          <t>6bfaef0a2c0b4fe1</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T23:00:00Z</t>
+          <t>2026-07-26T14:00:00Z</t>
         </is>
       </c>
       <c r="D102" s="24" t="inlineStr">
         <is>
-          <t>60600</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="E102" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F102" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="G102" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr">
@@ -29008,49 +29162,63 @@
         </is>
       </c>
       <c r="L102" s="26" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="M102" s="27" t="n">
-        <v>1.75188</v>
+        <v>2</v>
       </c>
       <c r="N102" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5</v>
       </c>
       <c r="O102" s="28" t="n">
-        <v>0.543543</v>
+        <v>0.769302</v>
       </c>
       <c r="P102" s="28" t="n"/>
       <c r="Q102" s="28" t="n">
-        <v>-0.027272</v>
+        <v>0.269302</v>
       </c>
       <c r="R102" s="26" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="S102" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U102" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V102" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W102" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T102" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U102" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V102" s="24" t="n"/>
-      <c r="W102" s="26" t="n"/>
-      <c r="X102" s="26" t="n"/>
+      <c r="X102" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y102" s="25" t="n"/>
       <c r="Z102" s="26" t="n"/>
       <c r="AA102" s="28" t="n"/>
       <c r="AB102" s="28" t="n"/>
-      <c r="AC102" s="30" t="n"/>
-      <c r="AD102" s="24" t="n"/>
+      <c r="AC102" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD102" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:39.939443Z</t>
+        </is>
+      </c>
       <c r="AE102" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-sr-dsg-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-sta-lc-2026-07-26).</t>
         </is>
       </c>
       <c r="AF102" s="31" t="inlineStr">
@@ -29060,7 +29228,7 @@
       </c>
       <c r="AG102" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH102" s="24" t="n"/>
@@ -29091,32 +29259,32 @@
       </c>
       <c r="AP102" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AQ102" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AR102" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AS102" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AT102" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AU102" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AV102" s="24" t="n"/>
@@ -29134,7 +29302,7 @@
       </c>
       <c r="BA102" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB102" s="24" t="inlineStr">
@@ -29144,12 +29312,12 @@
       </c>
       <c r="BC102" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD102" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE102" s="24" t="inlineStr">
@@ -29164,12 +29332,12 @@
       </c>
       <c r="BG102" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:15.656044Z</t>
+          <t>2026-07-26T12:49:44.422167Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29179,13 +29347,13 @@
       </c>
       <c r="BJ102" s="25" t="n"/>
       <c r="BK102" s="26" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="BL102" s="27" t="n">
-        <v>1.75188</v>
+        <v>2</v>
       </c>
       <c r="BM102" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5</v>
       </c>
       <c r="BN102" s="28" t="n"/>
       <c r="BO102" s="28" t="n"/>
@@ -29219,37 +29387,37 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>7c00f12d8e6c4a63</t>
+          <t>163f9b89282a4c61</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:00:00Z</t>
+          <t>2026-07-26T14:00:00Z</t>
         </is>
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>61033</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="G103" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr">
@@ -29259,7 +29427,7 @@
       </c>
       <c r="I103" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J103" s="25" t="n"/>
@@ -29269,49 +29437,63 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>108</v>
+        <v>-117</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>2.08</v>
+        <v>1.854701</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.539171</v>
       </c>
       <c r="O103" s="28" t="n">
-        <v>0.811601</v>
+        <v>0.518471</v>
       </c>
       <c r="P103" s="28" t="n"/>
       <c r="Q103" s="28" t="n">
-        <v>0.330832</v>
+        <v>-0.0207</v>
       </c>
       <c r="R103" s="26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="S103" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T103" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U103" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V103" s="24" t="n"/>
-      <c r="W103" s="26" t="n"/>
-      <c r="X103" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V103" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W103" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X103" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y103" s="25" t="n"/>
       <c r="Z103" s="26" t="n"/>
       <c r="AA103" s="28" t="n"/>
       <c r="AB103" s="28" t="n"/>
-      <c r="AC103" s="30" t="n"/>
-      <c r="AD103" s="24" t="n"/>
+      <c r="AC103" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD103" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:42.071753Z</t>
+        </is>
+      </c>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-bfx-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-sparta-atr-2026-07-26).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
@@ -29321,7 +29503,7 @@
       </c>
       <c r="AG103" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH103" s="24" t="n"/>
@@ -29352,32 +29534,32 @@
       </c>
       <c r="AP103" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AQ103" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AR103" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AS103" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AT103" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AU103" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AV103" s="24" t="n"/>
@@ -29395,7 +29577,7 @@
       </c>
       <c r="BA103" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB103" s="24" t="inlineStr">
@@ -29405,12 +29587,12 @@
       </c>
       <c r="BC103" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD103" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE103" s="24" t="inlineStr">
@@ -29425,12 +29607,12 @@
       </c>
       <c r="BG103" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:16.441993Z</t>
+          <t>2026-07-26T12:49:45.204211Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -29440,13 +29622,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>108</v>
+        <v>-117</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>2.08</v>
+        <v>1.854701</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.539171</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -29480,37 +29662,37 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>0220eb6d4fdb4afa</t>
+          <t>36f4eeb7a1fc4959</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:45:00Z</t>
+          <t>2026-07-26T15:00:00Z</t>
         </is>
       </c>
       <c r="D104" s="24" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="G104" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr">
@@ -29530,49 +29712,63 @@
         </is>
       </c>
       <c r="L104" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M104" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N104" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O104" s="28" t="n">
-        <v>0.608349</v>
+        <v>0.702966</v>
       </c>
       <c r="P104" s="28" t="n"/>
       <c r="Q104" s="28" t="n">
-        <v>-0.021281</v>
+        <v>0.062678</v>
       </c>
       <c r="R104" s="26" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="S104" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T104" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U104" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V104" s="24" t="n"/>
-      <c r="W104" s="26" t="n"/>
-      <c r="X104" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V104" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W104" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X104" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y104" s="25" t="n"/>
       <c r="Z104" s="26" t="n"/>
       <c r="AA104" s="28" t="n"/>
       <c r="AB104" s="28" t="n"/>
-      <c r="AC104" s="30" t="n"/>
-      <c r="AD104" s="24" t="n"/>
+      <c r="AC104" s="30" t="n">
+        <v>1.1236</v>
+      </c>
+      <c r="AD104" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:44.016789Z</t>
+        </is>
+      </c>
       <c r="AE104" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-dk-hle-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-wc-mglz-2026-07-26).</t>
         </is>
       </c>
       <c r="AF104" s="31" t="inlineStr">
@@ -29613,32 +29809,32 @@
       </c>
       <c r="AP104" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="AQ104" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="AR104" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="AS104" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="AT104" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="AU104" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="AV104" s="24" t="n"/>
@@ -29656,7 +29852,7 @@
       </c>
       <c r="BA104" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB104" s="24" t="inlineStr">
@@ -29666,12 +29862,12 @@
       </c>
       <c r="BC104" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD104" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE104" s="24" t="inlineStr">
@@ -29686,12 +29882,12 @@
       </c>
       <c r="BG104" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:17.204873Z</t>
+          <t>2026-07-26T12:49:46.102307Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -29701,13 +29897,13 @@
       </c>
       <c r="BJ104" s="25" t="n"/>
       <c r="BK104" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL104" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM104" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN104" s="28" t="n"/>
       <c r="BO104" s="28" t="n"/>
@@ -29741,37 +29937,37 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>0bbf1ee713f04f6c</t>
+          <t>525c1c2254fc4ad8</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T07:30:00Z</t>
+          <t>2026-07-26T15:00:00Z</t>
         </is>
       </c>
       <c r="D105" s="24" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>61671</t>
         </is>
       </c>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="G105" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr">
@@ -29781,7 +29977,7 @@
       </c>
       <c r="I105" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J105" s="25" t="n"/>
@@ -29791,20 +29987,20 @@
         </is>
       </c>
       <c r="L105" s="26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M105" s="27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="N105" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.359712</v>
       </c>
       <c r="O105" s="28" t="n">
-        <v>0.7097250000000001</v>
+        <v>0.786851</v>
       </c>
       <c r="P105" s="28" t="n"/>
       <c r="Q105" s="28" t="n">
-        <v>0.339355</v>
+        <v>0.427139</v>
       </c>
       <c r="R105" s="26" t="n">
         <v>100</v>
@@ -29814,26 +30010,40 @@
       </c>
       <c r="T105" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U105" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V105" s="24" t="n"/>
-      <c r="W105" s="26" t="n"/>
-      <c r="X105" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V105" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W105" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y105" s="25" t="n"/>
       <c r="Z105" s="26" t="n"/>
       <c r="AA105" s="28" t="n"/>
       <c r="AB105" s="28" t="n"/>
-      <c r="AC105" s="30" t="n"/>
-      <c r="AD105" s="24" t="n"/>
+      <c r="AC105" s="30" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD105" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:45.929698Z</t>
+        </is>
+      </c>
       <c r="AE105" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-kt-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-odk-ldp-2026-07-26).</t>
         </is>
       </c>
       <c r="AF105" s="31" t="inlineStr">
@@ -29874,32 +30084,32 @@
       </c>
       <c r="AP105" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AQ105" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AR105" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AS105" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AT105" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AU105" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AV105" s="24" t="n"/>
@@ -29917,7 +30127,7 @@
       </c>
       <c r="BA105" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB105" s="24" t="inlineStr">
@@ -29927,12 +30137,12 @@
       </c>
       <c r="BC105" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD105" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE105" s="24" t="inlineStr">
@@ -29947,12 +30157,12 @@
       </c>
       <c r="BG105" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:17.997008Z</t>
+          <t>2026-07-26T12:49:46.942100Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -29962,13 +30172,13 @@
       </c>
       <c r="BJ105" s="25" t="n"/>
       <c r="BK105" s="26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="BL105" s="27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BM105" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.359712</v>
       </c>
       <c r="BN105" s="28" t="n"/>
       <c r="BO105" s="28" t="n"/>
@@ -30002,37 +30212,37 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>817a93157d534d4e</t>
+          <t>88556ad9f9604bc9</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-26T15:30:00Z</t>
         </is>
       </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>61480</t>
         </is>
       </c>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>sleepers</t>
         </is>
       </c>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>aimclub</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
@@ -30061,21 +30271,21 @@
         <v>0.640288</v>
       </c>
       <c r="O106" s="28" t="n">
-        <v>0.6818</v>
+        <v>0.558205</v>
       </c>
       <c r="P106" s="28" t="n"/>
       <c r="Q106" s="28" t="n">
-        <v>0.041512</v>
+        <v>-0.082083</v>
       </c>
       <c r="R106" s="26" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S106" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T106" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U106" s="24" t="inlineStr">
@@ -30094,7 +30304,7 @@
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-t1a-nsea-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-aimc-sle-2026-07-26).</t>
         </is>
       </c>
       <c r="AF106" s="31" t="inlineStr">
@@ -30135,32 +30345,32 @@
       </c>
       <c r="AP106" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>sleepers</t>
         </is>
       </c>
       <c r="AQ106" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>sleepers</t>
         </is>
       </c>
       <c r="AR106" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>sleepers</t>
         </is>
       </c>
       <c r="AS106" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>aimclub</t>
         </is>
       </c>
       <c r="AT106" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>aimclub</t>
         </is>
       </c>
       <c r="AU106" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>aimclub</t>
         </is>
       </c>
       <c r="AV106" s="24" t="n"/>
@@ -30178,7 +30388,7 @@
       </c>
       <c r="BA106" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB106" s="24" t="inlineStr">
@@ -30188,12 +30398,12 @@
       </c>
       <c r="BC106" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD106" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE106" s="24" t="inlineStr">
@@ -30208,12 +30418,12 @@
       </c>
       <c r="BG106" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:18.841768Z</t>
+          <t>2026-07-26T12:49:48.845751Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30263,37 +30473,37 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>7af9d12b384040ee</t>
+          <t>1490f707da544484</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:15:00Z</t>
+          <t>2026-07-26T16:00:00Z</t>
         </is>
       </c>
       <c r="D107" s="24" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="G107" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr">
@@ -30303,7 +30513,7 @@
       </c>
       <c r="I107" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J107" s="25" t="n"/>
@@ -30313,30 +30523,30 @@
         </is>
       </c>
       <c r="L107" s="26" t="n">
-        <v>-178</v>
+        <v>113</v>
       </c>
       <c r="M107" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.13</v>
       </c>
       <c r="N107" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.469484</v>
       </c>
       <c r="O107" s="28" t="n">
-        <v>0.506725</v>
+        <v>0.665479</v>
       </c>
       <c r="P107" s="28" t="n"/>
       <c r="Q107" s="28" t="n">
-        <v>-0.133563</v>
+        <v>0.195995</v>
       </c>
       <c r="R107" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S107" s="29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T107" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U107" s="24" t="inlineStr">
@@ -30355,7 +30565,7 @@
       <c r="AD107" s="24" t="n"/>
       <c r="AE107" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-dk-t1-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-mgc-nip-2026-07-26).</t>
         </is>
       </c>
       <c r="AF107" s="31" t="inlineStr">
@@ -30396,32 +30606,32 @@
       </c>
       <c r="AP107" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AQ107" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AR107" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AS107" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="AT107" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="AU107" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="AV107" s="24" t="n"/>
@@ -30439,7 +30649,7 @@
       </c>
       <c r="BA107" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB107" s="24" t="inlineStr">
@@ -30449,12 +30659,12 @@
       </c>
       <c r="BC107" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD107" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE107" s="24" t="inlineStr">
@@ -30469,12 +30679,12 @@
       </c>
       <c r="BG107" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:19.622422Z</t>
+          <t>2026-07-26T12:49:49.664310Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -30484,13 +30694,13 @@
       </c>
       <c r="BJ107" s="25" t="n"/>
       <c r="BK107" s="26" t="n">
-        <v>-178</v>
+        <v>113</v>
       </c>
       <c r="BL107" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.13</v>
       </c>
       <c r="BM107" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.469484</v>
       </c>
       <c r="BN107" s="28" t="n"/>
       <c r="BO107" s="28" t="n"/>
@@ -30524,37 +30734,37 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>4f75ada13906452e</t>
+          <t>dc27f4a4fe824b06</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:00:00Z</t>
+          <t>2026-07-26T17:00:00Z</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>62237</t>
         </is>
       </c>
       <c r="E108" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="G108" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr">
@@ -30574,30 +30784,30 @@
         </is>
       </c>
       <c r="L108" s="26" t="n">
-        <v>133</v>
+        <v>-163</v>
       </c>
       <c r="M108" s="27" t="n">
-        <v>2.33</v>
+        <v>1.613497</v>
       </c>
       <c r="N108" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.619772</v>
       </c>
       <c r="O108" s="28" t="n">
-        <v>0.912307</v>
+        <v>0.700097</v>
       </c>
       <c r="P108" s="28" t="n"/>
       <c r="Q108" s="28" t="n">
-        <v>0.483122</v>
+        <v>0.08032499999999999</v>
       </c>
       <c r="R108" s="26" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="S108" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T108" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U108" s="24" t="inlineStr">
@@ -30616,7 +30826,7 @@
       <c r="AD108" s="24" t="n"/>
       <c r="AE108" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-hle-krx-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-hon-pg-2026-07-26).</t>
         </is>
       </c>
       <c r="AF108" s="31" t="inlineStr">
@@ -30657,32 +30867,32 @@
       </c>
       <c r="AP108" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="AQ108" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="AR108" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="AS108" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AT108" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AU108" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AV108" s="24" t="n"/>
@@ -30700,7 +30910,7 @@
       </c>
       <c r="BA108" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB108" s="24" t="inlineStr">
@@ -30710,12 +30920,12 @@
       </c>
       <c r="BC108" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD108" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE108" s="24" t="inlineStr">
@@ -30730,12 +30940,12 @@
       </c>
       <c r="BG108" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:20.448813Z</t>
+          <t>2026-07-26T12:49:51.560831Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -30745,13 +30955,13 @@
       </c>
       <c r="BJ108" s="25" t="n"/>
       <c r="BK108" s="26" t="n">
-        <v>133</v>
+        <v>-163</v>
       </c>
       <c r="BL108" s="27" t="n">
-        <v>2.33</v>
+        <v>1.613497</v>
       </c>
       <c r="BM108" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.619772</v>
       </c>
       <c r="BN108" s="28" t="n"/>
       <c r="BO108" s="28" t="n"/>
@@ -30785,37 +30995,37 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>0d2e4deccfa2412d</t>
+          <t>f495ec3fb35f4b05</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:45:00Z</t>
+          <t>2026-07-26T17:00:00Z</t>
         </is>
       </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>61034</t>
         </is>
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr">
@@ -30825,7 +31035,7 @@
       </c>
       <c r="I109" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J109" s="25" t="n"/>
@@ -30835,30 +31045,30 @@
         </is>
       </c>
       <c r="L109" s="26" t="n">
-        <v>-163</v>
+        <v>-138</v>
       </c>
       <c r="M109" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.724638</v>
       </c>
       <c r="N109" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.579832</v>
       </c>
       <c r="O109" s="28" t="n">
-        <v>0.865659</v>
+        <v>0.527474</v>
       </c>
       <c r="P109" s="28" t="n"/>
       <c r="Q109" s="28" t="n">
-        <v>0.245887</v>
+        <v>-0.052358</v>
       </c>
       <c r="R109" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S109" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T109" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U109" s="24" t="inlineStr">
@@ -30877,7 +31087,7 @@
       <c r="AD109" s="24" t="n"/>
       <c r="AE109" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-t1-ns-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-eac-atr-2026-07-26).</t>
         </is>
       </c>
       <c r="AF109" s="31" t="inlineStr">
@@ -30918,32 +31128,32 @@
       </c>
       <c r="AP109" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AQ109" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AR109" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AS109" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="AT109" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="AU109" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="AV109" s="24" t="n"/>
@@ -30961,7 +31171,7 @@
       </c>
       <c r="BA109" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB109" s="24" t="inlineStr">
@@ -30971,12 +31181,12 @@
       </c>
       <c r="BC109" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD109" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE109" s="24" t="inlineStr">
@@ -30991,12 +31201,12 @@
       </c>
       <c r="BG109" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:21.212140Z</t>
+          <t>2026-07-26T12:49:52.386615Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31006,13 +31216,13 @@
       </c>
       <c r="BJ109" s="25" t="n"/>
       <c r="BK109" s="26" t="n">
-        <v>-163</v>
+        <v>-138</v>
       </c>
       <c r="BL109" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.724638</v>
       </c>
       <c r="BM109" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.579832</v>
       </c>
       <c r="BN109" s="28" t="n"/>
       <c r="BO109" s="28" t="n"/>
@@ -31046,37 +31256,37 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>bcac23347bb64da9</t>
+          <t>5a0a26925c424ed2</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:00:00Z</t>
+          <t>2026-07-26T17:00:00Z</t>
         </is>
       </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
-          <t>60724</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="E110" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="G110" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr">
@@ -31086,7 +31296,7 @@
       </c>
       <c r="I110" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J110" s="25" t="n"/>
@@ -31096,30 +31306,30 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-223</v>
+        <v>108</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.08</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.480769</v>
       </c>
       <c r="O110" s="28" t="n">
-        <v>0.654791</v>
+        <v>0.758379</v>
       </c>
       <c r="P110" s="28" t="n"/>
       <c r="Q110" s="28" t="n">
-        <v>-0.035611</v>
+        <v>0.27761</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="S110" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T110" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U110" s="24" t="inlineStr">
@@ -31138,7 +31348,7 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-genga-foxy-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-lav-btf-2026-07-26).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
@@ -31179,32 +31389,32 @@
       </c>
       <c r="AP110" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AQ110" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AR110" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AS110" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AT110" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AU110" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AV110" s="24" t="n"/>
@@ -31222,7 +31432,7 @@
       </c>
       <c r="BA110" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB110" s="24" t="inlineStr">
@@ -31232,12 +31442,12 @@
       </c>
       <c r="BC110" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD110" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE110" s="24" t="inlineStr">
@@ -31252,12 +31462,12 @@
       </c>
       <c r="BG110" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:22.005575Z</t>
+          <t>2026-07-26T12:49:53.215216Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31267,13 +31477,13 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-223</v>
+        <v>108</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.08</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.480769</v>
       </c>
       <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
@@ -31307,37 +31517,37 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>d7fdb20e0ba74ee6</t>
+          <t>b196e991eecc4227</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:45.242095Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:30:00Z</t>
+          <t>2026-07-26T15:00:00Z</t>
         </is>
       </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>VALORANT</t>
         </is>
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="G111" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="H111" s="24" t="inlineStr">
@@ -31357,20 +31567,20 @@
         </is>
       </c>
       <c r="L111" s="26" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="M111" s="27" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="N111" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.390625</v>
       </c>
       <c r="O111" s="28" t="n">
-        <v>0.803091</v>
+        <v>0.7726229999999999</v>
       </c>
       <c r="P111" s="28" t="n"/>
       <c r="Q111" s="28" t="n">
-        <v>0.462955</v>
+        <v>0.381998</v>
       </c>
       <c r="R111" s="26" t="n">
         <v>100</v>
@@ -31380,26 +31590,40 @@
       </c>
       <c r="T111" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U111" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V111" s="24" t="n"/>
-      <c r="W111" s="26" t="n"/>
-      <c r="X111" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V111" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W111" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y111" s="25" t="n"/>
       <c r="Z111" s="26" t="n"/>
       <c r="AA111" s="28" t="n"/>
       <c r="AB111" s="28" t="n"/>
-      <c r="AC111" s="30" t="n"/>
-      <c r="AD111" s="24" t="n"/>
+      <c r="AC111" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD111" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:53.960881Z</t>
+        </is>
+      </c>
       <c r="AE111" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-bro-dk-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-bbl-navi-2026-07-26).</t>
         </is>
       </c>
       <c r="AF111" s="31" t="inlineStr">
@@ -31409,7 +31633,7 @@
       </c>
       <c r="AG111" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH111" s="24" t="n"/>
@@ -31440,32 +31664,32 @@
       </c>
       <c r="AP111" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AQ111" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AR111" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AS111" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AT111" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AU111" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AV111" s="24" t="n"/>
@@ -31483,7 +31707,7 @@
       </c>
       <c r="BA111" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
         </is>
       </c>
       <c r="BB111" s="24" t="inlineStr">
@@ -31493,12 +31717,12 @@
       </c>
       <c r="BC111" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD111" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
         </is>
       </c>
       <c r="BE111" s="24" t="inlineStr">
@@ -31513,12 +31737,12 @@
       </c>
       <c r="BG111" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:22.804506Z</t>
+          <t>2026-07-26T12:50:32.723645Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -31528,13 +31752,13 @@
       </c>
       <c r="BJ111" s="25" t="n"/>
       <c r="BK111" s="26" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="BL111" s="27" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="BM111" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.390625</v>
       </c>
       <c r="BN111" s="28" t="n"/>
       <c r="BO111" s="28" t="n"/>
@@ -31568,37 +31792,37 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>269e26788da8483b</t>
+          <t>a02cf80a68614277</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T17:57:12.724550Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T11:15:00Z</t>
+          <t>2026-07-26T18:15:00Z</t>
         </is>
       </c>
       <c r="D112" s="24" t="inlineStr">
         <is>
-          <t>60734</t>
+          <t>61472</t>
         </is>
       </c>
       <c r="E112" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="G112" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr">
@@ -31608,7 +31832,7 @@
       </c>
       <c r="I112" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J112" s="25" t="n"/>
@@ -31618,30 +31842,30 @@
         </is>
       </c>
       <c r="L112" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="M112" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="N112" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="O112" s="28" t="n">
-        <v>0.885173</v>
+        <v>0.703286</v>
       </c>
       <c r="P112" s="28" t="n"/>
       <c r="Q112" s="28" t="n">
-        <v>0.234823</v>
+        <v>0.043422</v>
       </c>
       <c r="R112" s="26" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="S112" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T112" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U112" s="24" t="inlineStr">
@@ -31660,7 +31884,7 @@
       <c r="AD112" s="24" t="n"/>
       <c r="AE112" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-t1-dns-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-agc-mel-2026-07-26).</t>
         </is>
       </c>
       <c r="AF112" s="31" t="inlineStr">
@@ -31678,7 +31902,7 @@
       <c r="AJ112" s="31" t="n"/>
       <c r="AK112" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL112" s="26" t="n">
@@ -31686,47 +31910,47 @@
       </c>
       <c r="AM112" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN112" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO112" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP112" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AQ112" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AR112" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AS112" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AT112" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AU112" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AV112" s="24" t="n"/>
@@ -31744,7 +31968,7 @@
       </c>
       <c r="BA112" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB112" s="24" t="inlineStr">
@@ -31754,12 +31978,12 @@
       </c>
       <c r="BC112" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD112" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE112" s="24" t="inlineStr">
@@ -31774,12 +31998,12 @@
       </c>
       <c r="BG112" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:23.643887Z</t>
+          <t>2026-07-26T17:57:02.105740Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -31789,13 +32013,13 @@
       </c>
       <c r="BJ112" s="25" t="n"/>
       <c r="BK112" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="BL112" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="BM112" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="BN112" s="28" t="n"/>
       <c r="BO112" s="28" t="n"/>
@@ -31829,37 +32053,37 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>1eb3d3a5046749fa</t>
+          <t>8a2105f8fa1d40f6</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T17:57:20.796477Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-07-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>62509</t>
         </is>
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>DOTA2</t>
         </is>
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Team Jenz</t>
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr">
@@ -31879,30 +32103,30 @@
         </is>
       </c>
       <c r="L113" s="26" t="n">
-        <v>-233</v>
+        <v>-178</v>
       </c>
       <c r="M113" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.561798</v>
       </c>
       <c r="N113" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.640288</v>
       </c>
       <c r="O113" s="28" t="n">
-        <v>0.712884</v>
+        <v>0.521452</v>
       </c>
       <c r="P113" s="28" t="n"/>
       <c r="Q113" s="28" t="n">
-        <v>0.013184</v>
+        <v>-0.118836</v>
       </c>
       <c r="R113" s="26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S113" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T113" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U113" s="24" t="inlineStr">
@@ -31921,7 +32145,7 @@
       <c r="AD113" s="24" t="n"/>
       <c r="AE113" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-tje-stx-2026-07-26).</t>
         </is>
       </c>
       <c r="AF113" s="31" t="inlineStr">
@@ -31939,7 +32163,7 @@
       <c r="AJ113" s="31" t="n"/>
       <c r="AK113" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL113" s="26" t="n">
@@ -31947,47 +32171,47 @@
       </c>
       <c r="AM113" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN113" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO113" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP113" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AQ113" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AR113" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AS113" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Team Jenz</t>
         </is>
       </c>
       <c r="AT113" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Team Jenz</t>
         </is>
       </c>
       <c r="AU113" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Team Jenz</t>
         </is>
       </c>
       <c r="AV113" s="24" t="n"/>
@@ -32005,7 +32229,7 @@
       </c>
       <c r="BA113" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
         </is>
       </c>
       <c r="BB113" s="24" t="inlineStr">
@@ -32015,12 +32239,12 @@
       </c>
       <c r="BC113" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD113" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
         </is>
       </c>
       <c r="BE113" s="24" t="inlineStr">
@@ -32035,12 +32259,12 @@
       </c>
       <c r="BG113" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:28.530374Z</t>
+          <t>2026-07-26T17:57:18.639736Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -32050,13 +32274,13 @@
       </c>
       <c r="BJ113" s="25" t="n"/>
       <c r="BK113" s="26" t="n">
-        <v>-233</v>
+        <v>-178</v>
       </c>
       <c r="BL113" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.561798</v>
       </c>
       <c r="BM113" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.640288</v>
       </c>
       <c r="BN113" s="28" t="n"/>
       <c r="BO113" s="28" t="n"/>
@@ -32090,37 +32314,37 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>86195cd6ef414a9d</t>
+          <t>ed9f7eff1e3e4d89</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T17:57:31.397830Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T14:00:00Z</t>
+          <t>2026-07-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
-          <t>61030</t>
+          <t>60215</t>
         </is>
       </c>
       <c r="E114" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>VALORANT</t>
         </is>
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="G114" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr">
@@ -32140,30 +32364,30 @@
         </is>
       </c>
       <c r="L114" s="26" t="n">
-        <v>-233</v>
+        <v>-122</v>
       </c>
       <c r="M114" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.819672</v>
       </c>
       <c r="N114" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.54955</v>
       </c>
       <c r="O114" s="28" t="n">
-        <v>0.603297</v>
+        <v>0.5200050000000001</v>
       </c>
       <c r="P114" s="28" t="n"/>
       <c r="Q114" s="28" t="n">
-        <v>-0.096403</v>
+        <v>-0.029545</v>
       </c>
       <c r="R114" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="S114" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="29" t="n">
-        <v>1.5</v>
-      </c>
       <c r="T114" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U114" s="24" t="inlineStr">
@@ -32182,7 +32406,7 @@
       <c r="AD114" s="24" t="n"/>
       <c r="AE114" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-inox-g2a-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-th-kc-2026-07-26).</t>
         </is>
       </c>
       <c r="AF114" s="31" t="inlineStr">
@@ -32200,7 +32424,7 @@
       <c r="AJ114" s="31" t="n"/>
       <c r="AK114" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL114" s="26" t="n">
@@ -32208,47 +32432,47 @@
       </c>
       <c r="AM114" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN114" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO114" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP114" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="AQ114" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="AR114" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="AS114" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AT114" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AU114" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AV114" s="24" t="n"/>
@@ -32266,7 +32490,7 @@
       </c>
       <c r="BA114" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
         </is>
       </c>
       <c r="BB114" s="24" t="inlineStr">
@@ -32276,12 +32500,12 @@
       </c>
       <c r="BC114" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD114" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
         </is>
       </c>
       <c r="BE114" s="24" t="inlineStr">
@@ -32296,12 +32520,12 @@
       </c>
       <c r="BG114" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:42.821812Z</t>
+          <t>2026-07-26T17:57:23.163200Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">
@@ -32311,13 +32535,13 @@
       </c>
       <c r="BJ114" s="25" t="n"/>
       <c r="BK114" s="26" t="n">
-        <v>-233</v>
+        <v>-122</v>
       </c>
       <c r="BL114" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.819672</v>
       </c>
       <c r="BM114" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.54955</v>
       </c>
       <c r="BN114" s="28" t="n"/>
       <c r="BO114" s="28" t="n"/>
@@ -32351,37 +32575,37 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="24" t="inlineStr">
         <is>
-          <t>6bfaef0a2c0b4fe1</t>
+          <t>6c4cf1f5db834912</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T14:00:00Z</t>
+          <t>2026-07-26T20:00:00Z</t>
         </is>
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>60465</t>
         </is>
       </c>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="G115" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="H115" s="24" t="inlineStr">
@@ -32401,30 +32625,30 @@
         </is>
       </c>
       <c r="L115" s="26" t="n">
-        <v>100</v>
+        <v>-144</v>
       </c>
       <c r="M115" s="27" t="n">
-        <v>2</v>
+        <v>1.694444</v>
       </c>
       <c r="N115" s="28" t="n">
-        <v>0.5</v>
+        <v>0.590164</v>
       </c>
       <c r="O115" s="28" t="n">
-        <v>0.769302</v>
+        <v>0.723066</v>
       </c>
       <c r="P115" s="28" t="n"/>
       <c r="Q115" s="28" t="n">
-        <v>0.269302</v>
+        <v>0.132902</v>
       </c>
       <c r="R115" s="26" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="S115" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T115" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U115" s="24" t="inlineStr">
@@ -32443,7 +32667,7 @@
       <c r="AD115" s="24" t="n"/>
       <c r="AE115" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-sta-lc-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-tl-c9-2026-07-26).</t>
         </is>
       </c>
       <c r="AF115" s="31" t="inlineStr">
@@ -32484,32 +32708,32 @@
       </c>
       <c r="AP115" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AQ115" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AR115" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AS115" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AT115" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AU115" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AV115" s="24" t="n"/>
@@ -32527,7 +32751,7 @@
       </c>
       <c r="BA115" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB115" s="24" t="inlineStr">
@@ -32537,12 +32761,12 @@
       </c>
       <c r="BC115" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD115" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE115" s="24" t="inlineStr">
@@ -32557,12 +32781,12 @@
       </c>
       <c r="BG115" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:44.422167Z</t>
+          <t>2026-07-26T18:26:40.383810Z</t>
         </is>
       </c>
       <c r="BI115" s="24" t="inlineStr">
@@ -32572,13 +32796,13 @@
       </c>
       <c r="BJ115" s="25" t="n"/>
       <c r="BK115" s="26" t="n">
-        <v>100</v>
+        <v>-144</v>
       </c>
       <c r="BL115" s="27" t="n">
-        <v>2</v>
+        <v>1.694444</v>
       </c>
       <c r="BM115" s="28" t="n">
-        <v>0.5</v>
+        <v>0.590164</v>
       </c>
       <c r="BN115" s="28" t="n"/>
       <c r="BO115" s="28" t="n"/>
@@ -32612,37 +32836,37 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>163f9b89282a4c61</t>
+          <t>b98fd7f46386455c</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T14:00:00Z</t>
+          <t>2026-07-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>60600</t>
         </is>
       </c>
       <c r="E116" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Disguised</t>
         </is>
       </c>
       <c r="G116" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Shopify Rebellion</t>
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr">
@@ -32662,30 +32886,30 @@
         </is>
       </c>
       <c r="L116" s="26" t="n">
-        <v>-117</v>
+        <v>-133</v>
       </c>
       <c r="M116" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.75188</v>
       </c>
       <c r="N116" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.570815</v>
       </c>
       <c r="O116" s="28" t="n">
-        <v>0.518471</v>
+        <v>0.543543</v>
       </c>
       <c r="P116" s="28" t="n"/>
       <c r="Q116" s="28" t="n">
-        <v>-0.0207</v>
+        <v>-0.027272</v>
       </c>
       <c r="R116" s="26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S116" s="29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T116" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U116" s="24" t="inlineStr">
@@ -32704,7 +32928,7 @@
       <c r="AD116" s="24" t="n"/>
       <c r="AE116" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-sparta-atr-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-sr-dsg-2026-07-26).</t>
         </is>
       </c>
       <c r="AF116" s="31" t="inlineStr">
@@ -32722,7 +32946,7 @@
       <c r="AJ116" s="31" t="n"/>
       <c r="AK116" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL116" s="26" t="n">
@@ -32730,47 +32954,47 @@
       </c>
       <c r="AM116" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN116" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO116" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP116" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Disguised</t>
         </is>
       </c>
       <c r="AQ116" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Disguised</t>
         </is>
       </c>
       <c r="AR116" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Disguised</t>
         </is>
       </c>
       <c r="AS116" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Shopify Rebellion</t>
         </is>
       </c>
       <c r="AT116" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Shopify Rebellion</t>
         </is>
       </c>
       <c r="AU116" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Shopify Rebellion</t>
         </is>
       </c>
       <c r="AV116" s="24" t="n"/>
@@ -32788,7 +33012,7 @@
       </c>
       <c r="BA116" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB116" s="24" t="inlineStr">
@@ -32798,12 +33022,12 @@
       </c>
       <c r="BC116" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD116" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE116" s="24" t="inlineStr">
@@ -32818,12 +33042,12 @@
       </c>
       <c r="BG116" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:45.204211Z</t>
+          <t>2026-07-26T18:26:40.862733Z</t>
         </is>
       </c>
       <c r="BI116" s="24" t="inlineStr">
@@ -32833,13 +33057,13 @@
       </c>
       <c r="BJ116" s="25" t="n"/>
       <c r="BK116" s="26" t="n">
-        <v>-117</v>
+        <v>-133</v>
       </c>
       <c r="BL116" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.75188</v>
       </c>
       <c r="BM116" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.570815</v>
       </c>
       <c r="BN116" s="28" t="n"/>
       <c r="BO116" s="28" t="n"/>
@@ -32873,37 +33097,37 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>36f4eeb7a1fc4959</t>
+          <t>7d898feb845e47a9</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:00:00Z</t>
+          <t>2026-07-27T06:00:00Z</t>
         </is>
       </c>
       <c r="D117" s="24" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="G117" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
@@ -32923,30 +33147,30 @@
         </is>
       </c>
       <c r="L117" s="26" t="n">
-        <v>-178</v>
+        <v>-108</v>
       </c>
       <c r="M117" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.925926</v>
       </c>
       <c r="N117" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.519231</v>
       </c>
       <c r="O117" s="28" t="n">
-        <v>0.702966</v>
+        <v>0.811601</v>
       </c>
       <c r="P117" s="28" t="n"/>
       <c r="Q117" s="28" t="n">
-        <v>0.062678</v>
+        <v>0.29237</v>
       </c>
       <c r="R117" s="26" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="S117" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T117" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U117" s="24" t="inlineStr">
@@ -32965,7 +33189,7 @@
       <c r="AD117" s="24" t="n"/>
       <c r="AE117" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-wc-mglz-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-bfx-gen-2026-07-27).</t>
         </is>
       </c>
       <c r="AF117" s="31" t="inlineStr">
@@ -33006,32 +33230,32 @@
       </c>
       <c r="AP117" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AQ117" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AR117" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AS117" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AT117" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AU117" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AV117" s="24" t="n"/>
@@ -33049,7 +33273,7 @@
       </c>
       <c r="BA117" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB117" s="24" t="inlineStr">
@@ -33059,12 +33283,12 @@
       </c>
       <c r="BC117" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD117" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE117" s="24" t="inlineStr">
@@ -33079,12 +33303,12 @@
       </c>
       <c r="BG117" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:46.102307Z</t>
+          <t>2026-07-26T18:26:41.407259Z</t>
         </is>
       </c>
       <c r="BI117" s="24" t="inlineStr">
@@ -33094,13 +33318,13 @@
       </c>
       <c r="BJ117" s="25" t="n"/>
       <c r="BK117" s="26" t="n">
-        <v>-178</v>
+        <v>-108</v>
       </c>
       <c r="BL117" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.925926</v>
       </c>
       <c r="BM117" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.519231</v>
       </c>
       <c r="BN117" s="28" t="n"/>
       <c r="BO117" s="28" t="n"/>
@@ -33134,37 +33358,37 @@
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="24" t="inlineStr">
         <is>
-          <t>525c1c2254fc4ad8</t>
+          <t>5062bd44b9df416a</t>
         </is>
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C118" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:00:00Z</t>
+          <t>2026-07-27T06:45:00Z</t>
         </is>
       </c>
       <c r="D118" s="24" t="inlineStr">
         <is>
-          <t>61671</t>
+          <t>60706</t>
         </is>
       </c>
       <c r="E118" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F118" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G118" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="H118" s="24" t="inlineStr">
@@ -33174,7 +33398,7 @@
       </c>
       <c r="I118" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J118" s="25" t="n"/>
@@ -33184,30 +33408,30 @@
         </is>
       </c>
       <c r="L118" s="26" t="n">
-        <v>178</v>
+        <v>-170</v>
       </c>
       <c r="M118" s="27" t="n">
-        <v>2.78</v>
+        <v>1.588235</v>
       </c>
       <c r="N118" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.62963</v>
       </c>
       <c r="O118" s="28" t="n">
-        <v>0.786851</v>
+        <v>0.608349</v>
       </c>
       <c r="P118" s="28" t="n"/>
       <c r="Q118" s="28" t="n">
-        <v>0.427139</v>
+        <v>-0.021281</v>
       </c>
       <c r="R118" s="26" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="S118" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T118" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U118" s="24" t="inlineStr">
@@ -33226,7 +33450,7 @@
       <c r="AD118" s="24" t="n"/>
       <c r="AE118" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-odk-ldp-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-dk-hle-2026-07-27).</t>
         </is>
       </c>
       <c r="AF118" s="31" t="inlineStr">
@@ -33244,7 +33468,7 @@
       <c r="AJ118" s="31" t="n"/>
       <c r="AK118" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL118" s="26" t="n">
@@ -33252,47 +33476,47 @@
       </c>
       <c r="AM118" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN118" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO118" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP118" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ118" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR118" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS118" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AT118" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AU118" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AV118" s="24" t="n"/>
@@ -33310,7 +33534,7 @@
       </c>
       <c r="BA118" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB118" s="24" t="inlineStr">
@@ -33320,12 +33544,12 @@
       </c>
       <c r="BC118" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD118" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE118" s="24" t="inlineStr">
@@ -33340,12 +33564,12 @@
       </c>
       <c r="BG118" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH118" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:46.942100Z</t>
+          <t>2026-07-26T18:26:41.925574Z</t>
         </is>
       </c>
       <c r="BI118" s="24" t="inlineStr">
@@ -33355,13 +33579,13 @@
       </c>
       <c r="BJ118" s="25" t="n"/>
       <c r="BK118" s="26" t="n">
-        <v>178</v>
+        <v>-170</v>
       </c>
       <c r="BL118" s="27" t="n">
-        <v>2.78</v>
+        <v>1.588235</v>
       </c>
       <c r="BM118" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.62963</v>
       </c>
       <c r="BN118" s="28" t="n"/>
       <c r="BO118" s="28" t="n"/>
@@ -33395,37 +33619,37 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="24" t="inlineStr">
         <is>
-          <t>88556ad9f9604bc9</t>
+          <t>411d08752d7649e7</t>
         </is>
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C119" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:30:00Z</t>
+          <t>2026-07-27T07:30:00Z</t>
         </is>
       </c>
       <c r="D119" s="24" t="inlineStr">
         <is>
-          <t>61480</t>
+          <t>60707</t>
         </is>
       </c>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F119" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="G119" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="H119" s="24" t="inlineStr">
@@ -33435,7 +33659,7 @@
       </c>
       <c r="I119" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J119" s="25" t="n"/>
@@ -33445,30 +33669,30 @@
         </is>
       </c>
       <c r="L119" s="26" t="n">
-        <v>-178</v>
+        <v>122</v>
       </c>
       <c r="M119" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.22</v>
       </c>
       <c r="N119" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.45045</v>
       </c>
       <c r="O119" s="28" t="n">
-        <v>0.558205</v>
+        <v>0.7097250000000001</v>
       </c>
       <c r="P119" s="28" t="n"/>
       <c r="Q119" s="28" t="n">
-        <v>-0.082083</v>
+        <v>0.259275</v>
       </c>
       <c r="R119" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S119" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T119" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U119" s="24" t="inlineStr">
@@ -33487,7 +33711,7 @@
       <c r="AD119" s="24" t="n"/>
       <c r="AE119" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-aimc-sle-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-kt-gen-2026-07-27).</t>
         </is>
       </c>
       <c r="AF119" s="31" t="inlineStr">
@@ -33528,32 +33752,32 @@
       </c>
       <c r="AP119" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AQ119" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AR119" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AS119" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="AT119" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="AU119" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="AV119" s="24" t="n"/>
@@ -33571,7 +33795,7 @@
       </c>
       <c r="BA119" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB119" s="24" t="inlineStr">
@@ -33581,12 +33805,12 @@
       </c>
       <c r="BC119" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD119" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE119" s="24" t="inlineStr">
@@ -33601,12 +33825,12 @@
       </c>
       <c r="BG119" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH119" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:48.845751Z</t>
+          <t>2026-07-26T18:26:42.528294Z</t>
         </is>
       </c>
       <c r="BI119" s="24" t="inlineStr">
@@ -33616,13 +33840,13 @@
       </c>
       <c r="BJ119" s="25" t="n"/>
       <c r="BK119" s="26" t="n">
-        <v>-178</v>
+        <v>122</v>
       </c>
       <c r="BL119" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.22</v>
       </c>
       <c r="BM119" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.45045</v>
       </c>
       <c r="BN119" s="28" t="n"/>
       <c r="BO119" s="28" t="n"/>
@@ -33656,37 +33880,37 @@
     <row r="120" ht="36" customHeight="1">
       <c r="A120" s="24" t="inlineStr">
         <is>
-          <t>1490f707da544484</t>
+          <t>dff7844bc77f4a47</t>
         </is>
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C120" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T16:00:00Z</t>
+          <t>2026-07-27T08:00:00Z</t>
         </is>
       </c>
       <c r="D120" s="24" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="E120" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F120" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="G120" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="H120" s="24" t="inlineStr">
@@ -33706,30 +33930,30 @@
         </is>
       </c>
       <c r="L120" s="26" t="n">
-        <v>113</v>
+        <v>-178</v>
       </c>
       <c r="M120" s="27" t="n">
-        <v>2.13</v>
+        <v>1.561798</v>
       </c>
       <c r="N120" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.640288</v>
       </c>
       <c r="O120" s="28" t="n">
-        <v>0.665479</v>
+        <v>0.6818</v>
       </c>
       <c r="P120" s="28" t="n"/>
       <c r="Q120" s="28" t="n">
-        <v>0.195995</v>
+        <v>0.041512</v>
       </c>
       <c r="R120" s="26" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S120" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T120" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U120" s="24" t="inlineStr">
@@ -33748,7 +33972,7 @@
       <c r="AD120" s="24" t="n"/>
       <c r="AE120" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-mgc-nip-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-t1a-nsea-2026-07-27).</t>
         </is>
       </c>
       <c r="AF120" s="31" t="inlineStr">
@@ -33789,32 +34013,32 @@
       </c>
       <c r="AP120" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AQ120" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AR120" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AS120" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="AT120" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="AU120" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="AV120" s="24" t="n"/>
@@ -33832,7 +34056,7 @@
       </c>
       <c r="BA120" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB120" s="24" t="inlineStr">
@@ -33842,12 +34066,12 @@
       </c>
       <c r="BC120" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD120" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE120" s="24" t="inlineStr">
@@ -33862,12 +34086,12 @@
       </c>
       <c r="BG120" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH120" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:49.664310Z</t>
+          <t>2026-07-26T18:26:43.057913Z</t>
         </is>
       </c>
       <c r="BI120" s="24" t="inlineStr">
@@ -33877,13 +34101,13 @@
       </c>
       <c r="BJ120" s="25" t="n"/>
       <c r="BK120" s="26" t="n">
-        <v>113</v>
+        <v>-178</v>
       </c>
       <c r="BL120" s="27" t="n">
-        <v>2.13</v>
+        <v>1.561798</v>
       </c>
       <c r="BM120" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.640288</v>
       </c>
       <c r="BN120" s="28" t="n"/>
       <c r="BO120" s="28" t="n"/>
@@ -33917,37 +34141,37 @@
     <row r="121" ht="36" customHeight="1">
       <c r="A121" s="24" t="inlineStr">
         <is>
-          <t>dc27f4a4fe824b06</t>
+          <t>f46f0328c3064c1f</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T17:00:00Z</t>
+          <t>2026-07-27T08:15:00Z</t>
         </is>
       </c>
       <c r="D121" s="24" t="inlineStr">
         <is>
-          <t>62237</t>
+          <t>60713</t>
         </is>
       </c>
       <c r="E121" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F121" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G121" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="H121" s="24" t="inlineStr">
@@ -33957,7 +34181,7 @@
       </c>
       <c r="I121" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J121" s="25" t="n"/>
@@ -33967,30 +34191,30 @@
         </is>
       </c>
       <c r="L121" s="26" t="n">
-        <v>-163</v>
+        <v>-178</v>
       </c>
       <c r="M121" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.561798</v>
       </c>
       <c r="N121" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.640288</v>
       </c>
       <c r="O121" s="28" t="n">
-        <v>0.700097</v>
+        <v>0.506725</v>
       </c>
       <c r="P121" s="28" t="n"/>
       <c r="Q121" s="28" t="n">
-        <v>0.08032499999999999</v>
+        <v>-0.133563</v>
       </c>
       <c r="R121" s="26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S121" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T121" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U121" s="24" t="inlineStr">
@@ -34009,7 +34233,7 @@
       <c r="AD121" s="24" t="n"/>
       <c r="AE121" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-hon-pg-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-dk-t1-2026-07-27).</t>
         </is>
       </c>
       <c r="AF121" s="31" t="inlineStr">
@@ -34027,7 +34251,7 @@
       <c r="AJ121" s="31" t="n"/>
       <c r="AK121" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL121" s="26" t="n">
@@ -34035,47 +34259,47 @@
       </c>
       <c r="AM121" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN121" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO121" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP121" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AQ121" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AR121" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AS121" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AT121" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AU121" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AV121" s="24" t="n"/>
@@ -34093,7 +34317,7 @@
       </c>
       <c r="BA121" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB121" s="24" t="inlineStr">
@@ -34103,12 +34327,12 @@
       </c>
       <c r="BC121" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD121" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE121" s="24" t="inlineStr">
@@ -34123,12 +34347,12 @@
       </c>
       <c r="BG121" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH121" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:51.560831Z</t>
+          <t>2026-07-26T18:26:43.599449Z</t>
         </is>
       </c>
       <c r="BI121" s="24" t="inlineStr">
@@ -34138,13 +34362,13 @@
       </c>
       <c r="BJ121" s="25" t="n"/>
       <c r="BK121" s="26" t="n">
-        <v>-163</v>
+        <v>-178</v>
       </c>
       <c r="BL121" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.561798</v>
       </c>
       <c r="BM121" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.640288</v>
       </c>
       <c r="BN121" s="28" t="n"/>
       <c r="BO121" s="28" t="n"/>
@@ -34178,37 +34402,37 @@
     <row r="122" ht="36" customHeight="1">
       <c r="A122" s="24" t="inlineStr">
         <is>
-          <t>f495ec3fb35f4b05</t>
+          <t>010b95c11c3f4b39</t>
         </is>
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C122" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T17:00:00Z</t>
+          <t>2026-07-27T09:00:00Z</t>
         </is>
       </c>
       <c r="D122" s="24" t="inlineStr">
         <is>
-          <t>61034</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="E122" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F122" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="G122" s="24" t="inlineStr">
         <is>
-          <t>Esport Academy Copenhagen</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="H122" s="24" t="inlineStr">
@@ -34218,7 +34442,7 @@
       </c>
       <c r="I122" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J122" s="25" t="n"/>
@@ -34228,30 +34452,30 @@
         </is>
       </c>
       <c r="L122" s="26" t="n">
-        <v>-138</v>
+        <v>113</v>
       </c>
       <c r="M122" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.13</v>
       </c>
       <c r="N122" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.469484</v>
       </c>
       <c r="O122" s="28" t="n">
-        <v>0.527474</v>
+        <v>0.912307</v>
       </c>
       <c r="P122" s="28" t="n"/>
       <c r="Q122" s="28" t="n">
-        <v>-0.052358</v>
+        <v>0.442823</v>
       </c>
       <c r="R122" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S122" s="29" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="T122" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U122" s="24" t="inlineStr">
@@ -34270,7 +34494,7 @@
       <c r="AD122" s="24" t="n"/>
       <c r="AE122" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-eac-atr-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-hle-krx-2026-07-27).</t>
         </is>
       </c>
       <c r="AF122" s="31" t="inlineStr">
@@ -34311,32 +34535,32 @@
       </c>
       <c r="AP122" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AQ122" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AR122" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AS122" s="24" t="inlineStr">
         <is>
-          <t>Esport Academy Copenhagen</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AT122" s="24" t="inlineStr">
         <is>
-          <t>Esport Academy Copenhagen</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AU122" s="24" t="inlineStr">
         <is>
-          <t>Esport Academy Copenhagen</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AV122" s="24" t="n"/>
@@ -34354,7 +34578,7 @@
       </c>
       <c r="BA122" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB122" s="24" t="inlineStr">
@@ -34364,12 +34588,12 @@
       </c>
       <c r="BC122" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD122" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE122" s="24" t="inlineStr">
@@ -34384,12 +34608,12 @@
       </c>
       <c r="BG122" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH122" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:52.386615Z</t>
+          <t>2026-07-26T18:26:44.171133Z</t>
         </is>
       </c>
       <c r="BI122" s="24" t="inlineStr">
@@ -34399,13 +34623,13 @@
       </c>
       <c r="BJ122" s="25" t="n"/>
       <c r="BK122" s="26" t="n">
-        <v>-138</v>
+        <v>113</v>
       </c>
       <c r="BL122" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.13</v>
       </c>
       <c r="BM122" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.469484</v>
       </c>
       <c r="BN122" s="28" t="n"/>
       <c r="BO122" s="28" t="n"/>
@@ -34439,37 +34663,37 @@
     <row r="123" ht="36" customHeight="1">
       <c r="A123" s="24" t="inlineStr">
         <is>
-          <t>5a0a26925c424ed2</t>
+          <t>c47366e8f0354da7</t>
         </is>
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C123" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T17:00:00Z</t>
+          <t>2026-07-27T09:45:00Z</t>
         </is>
       </c>
       <c r="D123" s="24" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="E123" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F123" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="G123" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="H123" s="24" t="inlineStr">
@@ -34489,20 +34713,20 @@
         </is>
       </c>
       <c r="L123" s="26" t="n">
-        <v>108</v>
+        <v>-203</v>
       </c>
       <c r="M123" s="27" t="n">
-        <v>2.08</v>
+        <v>1.492611</v>
       </c>
       <c r="N123" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.669967</v>
       </c>
       <c r="O123" s="28" t="n">
-        <v>0.758379</v>
+        <v>0.865659</v>
       </c>
       <c r="P123" s="28" t="n"/>
       <c r="Q123" s="28" t="n">
-        <v>0.27761</v>
+        <v>0.195692</v>
       </c>
       <c r="R123" s="26" t="n">
         <v>100</v>
@@ -34512,7 +34736,7 @@
       </c>
       <c r="T123" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U123" s="24" t="inlineStr">
@@ -34531,7 +34755,7 @@
       <c r="AD123" s="24" t="n"/>
       <c r="AE123" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-lav-btf-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-t1-ns-2026-07-27).</t>
         </is>
       </c>
       <c r="AF123" s="31" t="inlineStr">
@@ -34572,32 +34796,32 @@
       </c>
       <c r="AP123" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AQ123" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AR123" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AS123" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AT123" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AU123" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AV123" s="24" t="n"/>
@@ -34615,7 +34839,7 @@
       </c>
       <c r="BA123" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB123" s="24" t="inlineStr">
@@ -34625,12 +34849,12 @@
       </c>
       <c r="BC123" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD123" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE123" s="24" t="inlineStr">
@@ -34645,12 +34869,12 @@
       </c>
       <c r="BG123" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH123" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:53.215216Z</t>
+          <t>2026-07-26T18:26:44.707658Z</t>
         </is>
       </c>
       <c r="BI123" s="24" t="inlineStr">
@@ -34660,13 +34884,13 @@
       </c>
       <c r="BJ123" s="25" t="n"/>
       <c r="BK123" s="26" t="n">
-        <v>108</v>
+        <v>-203</v>
       </c>
       <c r="BL123" s="27" t="n">
-        <v>2.08</v>
+        <v>1.492611</v>
       </c>
       <c r="BM123" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.669967</v>
       </c>
       <c r="BN123" s="28" t="n"/>
       <c r="BO123" s="28" t="n"/>
@@ -34700,37 +34924,37 @@
     <row r="124" ht="36" customHeight="1">
       <c r="A124" s="24" t="inlineStr">
         <is>
-          <t>9c16abce53424df0</t>
+          <t>7aaf67eca20345a2</t>
         </is>
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C124" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T18:15:00Z</t>
+          <t>2026-07-27T10:00:00Z</t>
         </is>
       </c>
       <c r="D124" s="24" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>60724</t>
         </is>
       </c>
       <c r="E124" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F124" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="G124" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Gen.G Global Academy</t>
         </is>
       </c>
       <c r="H124" s="24" t="inlineStr">
@@ -34759,21 +34983,21 @@
         <v>0.690402</v>
       </c>
       <c r="O124" s="28" t="n">
-        <v>0.703286</v>
+        <v>0.654791</v>
       </c>
       <c r="P124" s="28" t="n"/>
       <c r="Q124" s="28" t="n">
-        <v>0.012884</v>
+        <v>-0.035611</v>
       </c>
       <c r="R124" s="26" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="S124" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T124" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U124" s="24" t="inlineStr">
@@ -34792,7 +35016,7 @@
       <c r="AD124" s="24" t="n"/>
       <c r="AE124" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-agc-mel-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-genga-foxy-2026-07-27).</t>
         </is>
       </c>
       <c r="AF124" s="31" t="inlineStr">
@@ -34810,7 +35034,7 @@
       <c r="AJ124" s="31" t="n"/>
       <c r="AK124" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL124" s="26" t="n">
@@ -34818,47 +35042,47 @@
       </c>
       <c r="AM124" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN124" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO124" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP124" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AQ124" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AR124" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AS124" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Gen.G Global Academy</t>
         </is>
       </c>
       <c r="AT124" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Gen.G Global Academy</t>
         </is>
       </c>
       <c r="AU124" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Gen.G Global Academy</t>
         </is>
       </c>
       <c r="AV124" s="24" t="n"/>
@@ -34876,7 +35100,7 @@
       </c>
       <c r="BA124" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB124" s="24" t="inlineStr">
@@ -34886,12 +35110,12 @@
       </c>
       <c r="BC124" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD124" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE124" s="24" t="inlineStr">
@@ -34906,12 +35130,12 @@
       </c>
       <c r="BG124" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH124" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:56.663548Z</t>
+          <t>2026-07-26T18:26:45.207143Z</t>
         </is>
       </c>
       <c r="BI124" s="24" t="inlineStr">
@@ -34961,37 +35185,37 @@
     <row r="125" ht="36" customHeight="1">
       <c r="A125" s="24" t="inlineStr">
         <is>
-          <t>968d52478f4a4d51</t>
+          <t>d57bc766fcf64ada</t>
         </is>
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-27T10:30:00Z</t>
         </is>
       </c>
       <c r="D125" s="24" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="E125" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F125" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="G125" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="H125" s="24" t="inlineStr">
@@ -35011,30 +35235,30 @@
         </is>
       </c>
       <c r="L125" s="26" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="M125" s="27" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="N125" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.340136</v>
       </c>
       <c r="O125" s="28" t="n">
-        <v>0.607321</v>
+        <v>0.803091</v>
       </c>
       <c r="P125" s="28" t="n"/>
       <c r="Q125" s="28" t="n">
-        <v>0.227093</v>
+        <v>0.462955</v>
       </c>
       <c r="R125" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S125" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T125" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U125" s="24" t="inlineStr">
@@ -35053,7 +35277,7 @@
       <c r="AD125" s="24" t="n"/>
       <c r="AE125" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-erx-ent-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-bro-dk-2026-07-27).</t>
         </is>
       </c>
       <c r="AF125" s="31" t="inlineStr">
@@ -35094,32 +35318,32 @@
       </c>
       <c r="AP125" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AQ125" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AR125" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AS125" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AT125" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AU125" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AV125" s="24" t="n"/>
@@ -35137,7 +35361,7 @@
       </c>
       <c r="BA125" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB125" s="24" t="inlineStr">
@@ -35147,12 +35371,12 @@
       </c>
       <c r="BC125" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD125" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE125" s="24" t="inlineStr">
@@ -35167,12 +35391,12 @@
       </c>
       <c r="BG125" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH125" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:59.220544Z</t>
+          <t>2026-07-26T18:26:45.912908Z</t>
         </is>
       </c>
       <c r="BI125" s="24" t="inlineStr">
@@ -35182,13 +35406,13 @@
       </c>
       <c r="BJ125" s="25" t="n"/>
       <c r="BK125" s="26" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="BL125" s="27" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="BM125" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.340136</v>
       </c>
       <c r="BN125" s="28" t="n"/>
       <c r="BO125" s="28" t="n"/>
@@ -35222,37 +35446,37 @@
     <row r="126" ht="36" customHeight="1">
       <c r="A126" s="24" t="inlineStr">
         <is>
-          <t>89d06030539145df</t>
+          <t>b2c0b40c125e4dcf</t>
         </is>
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C126" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T11:00:00Z</t>
+          <t>2026-07-27T21:00:00Z</t>
         </is>
       </c>
       <c r="D126" s="24" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>61044</t>
         </is>
       </c>
       <c r="E126" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F126" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="G126" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="H126" s="24" t="inlineStr">
@@ -35272,30 +35496,30 @@
         </is>
       </c>
       <c r="L126" s="26" t="n">
-        <v>-170</v>
+        <v>-233</v>
       </c>
       <c r="M126" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.429185</v>
       </c>
       <c r="N126" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.6997</v>
       </c>
       <c r="O126" s="28" t="n">
-        <v>0.736846</v>
+        <v>0.712884</v>
       </c>
       <c r="P126" s="28" t="n"/>
       <c r="Q126" s="28" t="n">
-        <v>0.107216</v>
+        <v>0.013184</v>
       </c>
       <c r="R126" s="26" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="S126" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T126" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U126" s="24" t="inlineStr">
@@ -35314,7 +35538,7 @@
       <c r="AD126" s="24" t="n"/>
       <c r="AE126" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
         </is>
       </c>
       <c r="AF126" s="31" t="inlineStr">
@@ -35355,32 +35579,32 @@
       </c>
       <c r="AP126" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AQ126" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AR126" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AS126" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AT126" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AU126" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AV126" s="24" t="n"/>
@@ -35398,7 +35622,7 @@
       </c>
       <c r="BA126" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB126" s="24" t="inlineStr">
@@ -35408,12 +35632,12 @@
       </c>
       <c r="BC126" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD126" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE126" s="24" t="inlineStr">
@@ -35428,12 +35652,12 @@
       </c>
       <c r="BG126" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH126" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:00.851568Z</t>
+          <t>2026-07-26T18:26:50.385656Z</t>
         </is>
       </c>
       <c r="BI126" s="24" t="inlineStr">
@@ -35443,13 +35667,13 @@
       </c>
       <c r="BJ126" s="25" t="n"/>
       <c r="BK126" s="26" t="n">
-        <v>-170</v>
+        <v>-233</v>
       </c>
       <c r="BL126" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.429185</v>
       </c>
       <c r="BM126" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.6997</v>
       </c>
       <c r="BN126" s="28" t="n"/>
       <c r="BO126" s="28" t="n"/>
@@ -35483,22 +35707,22 @@
     <row r="127" ht="36" customHeight="1">
       <c r="A127" s="24" t="inlineStr">
         <is>
-          <t>1f4025c17ddf4e52</t>
+          <t>aa01428f43df456c</t>
         </is>
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T11:00:00Z</t>
+          <t>2026-07-27T08:00:00Z</t>
         </is>
       </c>
       <c r="D127" s="24" t="inlineStr">
         <is>
-          <t>60729</t>
+          <t>60702</t>
         </is>
       </c>
       <c r="E127" s="24" t="inlineStr">
@@ -35508,12 +35732,12 @@
       </c>
       <c r="F127" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="G127" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H127" s="24" t="inlineStr">
@@ -35523,7 +35747,7 @@
       </c>
       <c r="I127" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J127" s="25" t="n"/>
@@ -35533,26 +35757,26 @@
         </is>
       </c>
       <c r="L127" s="26" t="n">
-        <v>-150</v>
+        <v>163</v>
       </c>
       <c r="M127" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.63</v>
       </c>
       <c r="N127" s="28" t="n">
-        <v>0.6</v>
+        <v>0.380228</v>
       </c>
       <c r="O127" s="28" t="n">
-        <v>0.539211</v>
+        <v>0.607321</v>
       </c>
       <c r="P127" s="28" t="n"/>
       <c r="Q127" s="28" t="n">
-        <v>-0.060789</v>
+        <v>0.227093</v>
       </c>
       <c r="R127" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S127" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T127" s="24" t="inlineStr">
         <is>
@@ -35575,7 +35799,7 @@
       <c r="AD127" s="24" t="n"/>
       <c r="AE127" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-unity-mta-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-erx-ent-2026-07-27).</t>
         </is>
       </c>
       <c r="AF127" s="31" t="inlineStr">
@@ -35616,32 +35840,32 @@
       </c>
       <c r="AP127" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AQ127" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AR127" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AS127" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT127" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU127" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV127" s="24" t="n"/>
@@ -35694,7 +35918,7 @@
       </c>
       <c r="BH127" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:01.643224Z</t>
+          <t>2026-07-26T18:27:02.006109Z</t>
         </is>
       </c>
       <c r="BI127" s="24" t="inlineStr">
@@ -35704,13 +35928,13 @@
       </c>
       <c r="BJ127" s="25" t="n"/>
       <c r="BK127" s="26" t="n">
-        <v>-150</v>
+        <v>163</v>
       </c>
       <c r="BL127" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.63</v>
       </c>
       <c r="BM127" s="28" t="n">
-        <v>0.6</v>
+        <v>0.380228</v>
       </c>
       <c r="BN127" s="28" t="n"/>
       <c r="BO127" s="28" t="n"/>
@@ -35744,22 +35968,22 @@
     <row r="128" ht="36" customHeight="1">
       <c r="A128" s="24" t="inlineStr">
         <is>
-          <t>c4b6378f46b44a6b</t>
+          <t>aab631e67e724cb9</t>
         </is>
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C128" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T14:00:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D128" s="24" t="inlineStr">
         <is>
-          <t>60748</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="E128" s="24" t="inlineStr">
@@ -35769,12 +35993,12 @@
       </c>
       <c r="F128" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G128" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="H128" s="24" t="inlineStr">
@@ -35794,26 +36018,26 @@
         </is>
       </c>
       <c r="L128" s="26" t="n">
-        <v>-213</v>
+        <v>-170</v>
       </c>
       <c r="M128" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.588235</v>
       </c>
       <c r="N128" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.62963</v>
       </c>
       <c r="O128" s="28" t="n">
-        <v>0.531101</v>
+        <v>0.736846</v>
       </c>
       <c r="P128" s="28" t="n"/>
       <c r="Q128" s="28" t="n">
-        <v>-0.14941</v>
+        <v>0.107216</v>
       </c>
       <c r="R128" s="26" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="S128" s="29" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="T128" s="24" t="inlineStr">
         <is>
@@ -35836,7 +36060,7 @@
       <c r="AD128" s="24" t="n"/>
       <c r="AE128" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-bpl-misa-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
         </is>
       </c>
       <c r="AF128" s="31" t="inlineStr">
@@ -35877,32 +36101,32 @@
       </c>
       <c r="AP128" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ128" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR128" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS128" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AT128" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AU128" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AV128" s="24" t="n"/>
@@ -35955,7 +36179,7 @@
       </c>
       <c r="BH128" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:05.947250Z</t>
+          <t>2026-07-26T18:27:02.997218Z</t>
         </is>
       </c>
       <c r="BI128" s="24" t="inlineStr">
@@ -35965,13 +36189,13 @@
       </c>
       <c r="BJ128" s="25" t="n"/>
       <c r="BK128" s="26" t="n">
-        <v>-213</v>
+        <v>-170</v>
       </c>
       <c r="BL128" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.588235</v>
       </c>
       <c r="BM128" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.62963</v>
       </c>
       <c r="BN128" s="28" t="n"/>
       <c r="BO128" s="28" t="n"/>
@@ -36005,22 +36229,22 @@
     <row r="129" ht="36" customHeight="1">
       <c r="A129" s="24" t="inlineStr">
         <is>
-          <t>e837e63515974bc1</t>
+          <t>7e9009bde4804d9b</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C129" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:30:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D129" s="24" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>60729</t>
         </is>
       </c>
       <c r="E129" s="24" t="inlineStr">
@@ -36030,12 +36254,12 @@
       </c>
       <c r="F129" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="G129" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="H129" s="24" t="inlineStr">
@@ -36055,26 +36279,26 @@
         </is>
       </c>
       <c r="L129" s="26" t="n">
-        <v>-194</v>
+        <v>-163</v>
       </c>
       <c r="M129" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.613497</v>
       </c>
       <c r="N129" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.619772</v>
       </c>
       <c r="O129" s="28" t="n">
-        <v>0.735192</v>
+        <v>0.539211</v>
       </c>
       <c r="P129" s="28" t="n"/>
       <c r="Q129" s="28" t="n">
-        <v>0.07532800000000001</v>
+        <v>-0.08056099999999999</v>
       </c>
       <c r="R129" s="26" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S129" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T129" s="24" t="inlineStr">
         <is>
@@ -36097,7 +36321,7 @@
       <c r="AD129" s="24" t="n"/>
       <c r="AE129" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-brute-navij-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-unity-mta-2026-07-27).</t>
         </is>
       </c>
       <c r="AF129" s="31" t="inlineStr">
@@ -36115,7 +36339,7 @@
       <c r="AJ129" s="31" t="n"/>
       <c r="AK129" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL129" s="26" t="n">
@@ -36123,47 +36347,47 @@
       </c>
       <c r="AM129" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN129" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO129" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP129" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AQ129" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AR129" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AS129" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AT129" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AU129" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AV129" s="24" t="n"/>
@@ -36216,7 +36440,7 @@
       </c>
       <c r="BH129" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:08.444139Z</t>
+          <t>2026-07-26T18:27:10.356558Z</t>
         </is>
       </c>
       <c r="BI129" s="24" t="inlineStr">
@@ -36226,13 +36450,13 @@
       </c>
       <c r="BJ129" s="25" t="n"/>
       <c r="BK129" s="26" t="n">
-        <v>-194</v>
+        <v>-163</v>
       </c>
       <c r="BL129" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.613497</v>
       </c>
       <c r="BM129" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.619772</v>
       </c>
       <c r="BN129" s="28" t="n"/>
       <c r="BO129" s="28" t="n"/>
@@ -36266,22 +36490,22 @@
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="24" t="inlineStr">
         <is>
-          <t>283950659df2466d</t>
+          <t>556ef5650a754cc4</t>
         </is>
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C130" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:00Z</t>
+          <t>2026-07-27T14:00:00Z</t>
         </is>
       </c>
       <c r="D130" s="24" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>60748</t>
         </is>
       </c>
       <c r="E130" s="24" t="inlineStr">
@@ -36291,12 +36515,12 @@
       </c>
       <c r="F130" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="G130" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="H130" s="24" t="inlineStr">
@@ -36316,26 +36540,26 @@
         </is>
       </c>
       <c r="L130" s="26" t="n">
-        <v>-156</v>
+        <v>-203</v>
       </c>
       <c r="M130" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.492611</v>
       </c>
       <c r="N130" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.669967</v>
       </c>
       <c r="O130" s="28" t="n">
-        <v>0.659512</v>
+        <v>0.531101</v>
       </c>
       <c r="P130" s="28" t="n"/>
       <c r="Q130" s="28" t="n">
-        <v>0.050137</v>
+        <v>-0.138866</v>
       </c>
       <c r="R130" s="26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S130" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T130" s="24" t="inlineStr">
         <is>
@@ -36358,7 +36582,7 @@
       <c r="AD130" s="24" t="n"/>
       <c r="AE130" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-bpl-misa-2026-07-27).</t>
         </is>
       </c>
       <c r="AF130" s="31" t="inlineStr">
@@ -36376,7 +36600,7 @@
       <c r="AJ130" s="31" t="n"/>
       <c r="AK130" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL130" s="26" t="n">
@@ -36384,47 +36608,47 @@
       </c>
       <c r="AM130" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN130" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO130" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP130" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AQ130" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AR130" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AS130" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AT130" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AU130" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AV130" s="24" t="n"/>
@@ -36477,7 +36701,7 @@
       </c>
       <c r="BH130" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:09.212122Z</t>
+          <t>2026-07-26T18:27:13.669585Z</t>
         </is>
       </c>
       <c r="BI130" s="24" t="inlineStr">
@@ -36487,13 +36711,13 @@
       </c>
       <c r="BJ130" s="25" t="n"/>
       <c r="BK130" s="26" t="n">
-        <v>-156</v>
+        <v>-203</v>
       </c>
       <c r="BL130" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.492611</v>
       </c>
       <c r="BM130" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.669967</v>
       </c>
       <c r="BN130" s="28" t="n"/>
       <c r="BO130" s="28" t="n"/>
@@ -36527,22 +36751,22 @@
     <row r="131" ht="36" customHeight="1">
       <c r="A131" s="24" t="inlineStr">
         <is>
-          <t>7222d72d98624c58</t>
+          <t>ee105543659d413b</t>
         </is>
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:00:00Z</t>
+          <t>2026-07-27T15:30:00Z</t>
         </is>
       </c>
       <c r="D131" s="24" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="E131" s="24" t="inlineStr">
@@ -36552,12 +36776,12 @@
       </c>
       <c r="F131" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="G131" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="H131" s="24" t="inlineStr">
@@ -36577,23 +36801,23 @@
         </is>
       </c>
       <c r="L131" s="26" t="n">
-        <v>-163</v>
+        <v>-194</v>
       </c>
       <c r="M131" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.515464</v>
       </c>
       <c r="N131" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.659864</v>
       </c>
       <c r="O131" s="28" t="n">
-        <v>0.70196</v>
+        <v>0.735192</v>
       </c>
       <c r="P131" s="28" t="n"/>
       <c r="Q131" s="28" t="n">
-        <v>0.082188</v>
+        <v>0.07532800000000001</v>
       </c>
       <c r="R131" s="26" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S131" s="29" t="n">
         <v>2</v>
@@ -36619,7 +36843,7 @@
       <c r="AD131" s="24" t="n"/>
       <c r="AE131" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-brute-navij-2026-07-27).</t>
         </is>
       </c>
       <c r="AF131" s="31" t="inlineStr">
@@ -36660,32 +36884,32 @@
       </c>
       <c r="AP131" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AQ131" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AR131" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AS131" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AT131" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AU131" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AV131" s="24" t="n"/>
@@ -36738,7 +36962,7 @@
       </c>
       <c r="BH131" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:09.997048Z</t>
+          <t>2026-07-26T18:27:15.414223Z</t>
         </is>
       </c>
       <c r="BI131" s="24" t="inlineStr">
@@ -36748,13 +36972,13 @@
       </c>
       <c r="BJ131" s="25" t="n"/>
       <c r="BK131" s="26" t="n">
-        <v>-163</v>
+        <v>-194</v>
       </c>
       <c r="BL131" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.515464</v>
       </c>
       <c r="BM131" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.659864</v>
       </c>
       <c r="BN131" s="28" t="n"/>
       <c r="BO131" s="28" t="n"/>
@@ -36788,22 +37012,22 @@
     <row r="132" ht="36" customHeight="1">
       <c r="A132" s="24" t="inlineStr">
         <is>
-          <t>6e1b7448185c430f</t>
+          <t>07dcca7769a24cd4</t>
         </is>
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C132" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:00:00Z</t>
+          <t>2026-07-27T16:30:00Z</t>
         </is>
       </c>
       <c r="D132" s="24" t="inlineStr">
         <is>
-          <t>60794</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="E132" s="24" t="inlineStr">
@@ -36813,12 +37037,12 @@
       </c>
       <c r="F132" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="G132" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="H132" s="24" t="inlineStr">
@@ -36828,7 +37052,7 @@
       </c>
       <c r="I132" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J132" s="25" t="n"/>
@@ -36838,26 +37062,26 @@
         </is>
       </c>
       <c r="L132" s="26" t="n">
-        <v>178</v>
+        <v>-156</v>
       </c>
       <c r="M132" s="27" t="n">
-        <v>2.78</v>
+        <v>1.641026</v>
       </c>
       <c r="N132" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.609375</v>
       </c>
       <c r="O132" s="28" t="n">
-        <v>0.573171</v>
+        <v>0.659512</v>
       </c>
       <c r="P132" s="28" t="n"/>
       <c r="Q132" s="28" t="n">
-        <v>0.213459</v>
+        <v>0.050137</v>
       </c>
       <c r="R132" s="26" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="S132" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T132" s="24" t="inlineStr">
         <is>
@@ -36880,7 +37104,7 @@
       <c r="AD132" s="24" t="n"/>
       <c r="AE132" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
         </is>
       </c>
       <c r="AF132" s="31" t="inlineStr">
@@ -36921,32 +37145,32 @@
       </c>
       <c r="AP132" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AQ132" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AR132" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AS132" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AT132" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AU132" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AV132" s="24" t="n"/>
@@ -36999,7 +37223,7 @@
       </c>
       <c r="BH132" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:10.787657Z</t>
+          <t>2026-07-26T18:27:16.097256Z</t>
         </is>
       </c>
       <c r="BI132" s="24" t="inlineStr">
@@ -37009,13 +37233,13 @@
       </c>
       <c r="BJ132" s="25" t="n"/>
       <c r="BK132" s="26" t="n">
-        <v>178</v>
+        <v>-156</v>
       </c>
       <c r="BL132" s="27" t="n">
-        <v>2.78</v>
+        <v>1.641026</v>
       </c>
       <c r="BM132" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.609375</v>
       </c>
       <c r="BN132" s="28" t="n"/>
       <c r="BO132" s="28" t="n"/>
@@ -37049,22 +37273,22 @@
     <row r="133" ht="36" customHeight="1">
       <c r="A133" s="24" t="inlineStr">
         <is>
-          <t>8a7fe5e3bdba4e60</t>
+          <t>8a82cac315d34213</t>
         </is>
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:30:00Z</t>
+          <t>2026-07-27T17:00:00Z</t>
         </is>
       </c>
       <c r="D133" s="24" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>60794</t>
         </is>
       </c>
       <c r="E133" s="24" t="inlineStr">
@@ -37074,12 +37298,12 @@
       </c>
       <c r="F133" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="G133" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="H133" s="24" t="inlineStr">
@@ -37099,26 +37323,26 @@
         </is>
       </c>
       <c r="L133" s="26" t="n">
-        <v>-156</v>
+        <v>178</v>
       </c>
       <c r="M133" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.78</v>
       </c>
       <c r="N133" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.359712</v>
       </c>
       <c r="O133" s="28" t="n">
-        <v>0.55859</v>
+        <v>0.573171</v>
       </c>
       <c r="P133" s="28" t="n"/>
       <c r="Q133" s="28" t="n">
-        <v>-0.050785</v>
+        <v>0.213459</v>
       </c>
       <c r="R133" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S133" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T133" s="24" t="inlineStr">
         <is>
@@ -37141,7 +37365,7 @@
       <c r="AD133" s="24" t="n"/>
       <c r="AE133" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-navij-mouzn-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
         </is>
       </c>
       <c r="AF133" s="31" t="inlineStr">
@@ -37182,32 +37406,32 @@
       </c>
       <c r="AP133" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="AQ133" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="AR133" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="AS133" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AT133" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AU133" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AV133" s="24" t="n"/>
@@ -37260,7 +37484,7 @@
       </c>
       <c r="BH133" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:11.590131Z</t>
+          <t>2026-07-26T18:27:16.598199Z</t>
         </is>
       </c>
       <c r="BI133" s="24" t="inlineStr">
@@ -37270,13 +37494,13 @@
       </c>
       <c r="BJ133" s="25" t="n"/>
       <c r="BK133" s="26" t="n">
-        <v>-156</v>
+        <v>178</v>
       </c>
       <c r="BL133" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.78</v>
       </c>
       <c r="BM133" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.359712</v>
       </c>
       <c r="BN133" s="28" t="n"/>
       <c r="BO133" s="28" t="n"/>
@@ -37310,37 +37534,37 @@
     <row r="134" ht="36" customHeight="1">
       <c r="A134" s="24" t="inlineStr">
         <is>
-          <t>b196e991eecc4227</t>
+          <t>93c25f8631334355</t>
         </is>
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:45.242095Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C134" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:00:00Z</t>
+          <t>2026-07-27T17:00:00Z</t>
         </is>
       </c>
       <c r="D134" s="24" t="inlineStr">
         <is>
-          <t>60136</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="E134" s="24" t="inlineStr">
         <is>
-          <t>VALORANT</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F134" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="G134" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="H134" s="24" t="inlineStr">
@@ -37350,7 +37574,7 @@
       </c>
       <c r="I134" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J134" s="25" t="n"/>
@@ -37360,30 +37584,30 @@
         </is>
       </c>
       <c r="L134" s="26" t="n">
-        <v>156</v>
+        <v>-163</v>
       </c>
       <c r="M134" s="27" t="n">
-        <v>2.56</v>
+        <v>1.613497</v>
       </c>
       <c r="N134" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.619772</v>
       </c>
       <c r="O134" s="28" t="n">
-        <v>0.7726229999999999</v>
+        <v>0.70196</v>
       </c>
       <c r="P134" s="28" t="n"/>
       <c r="Q134" s="28" t="n">
-        <v>0.381998</v>
+        <v>0.082188</v>
       </c>
       <c r="R134" s="26" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S134" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T134" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U134" s="24" t="inlineStr">
@@ -37402,7 +37626,7 @@
       <c r="AD134" s="24" t="n"/>
       <c r="AE134" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-bbl-navi-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
         </is>
       </c>
       <c r="AF134" s="31" t="inlineStr">
@@ -37443,32 +37667,32 @@
       </c>
       <c r="AP134" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AQ134" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AR134" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AS134" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AT134" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AU134" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AV134" s="24" t="n"/>
@@ -37486,7 +37710,7 @@
       </c>
       <c r="BA134" s="24" t="inlineStr">
         <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB134" s="24" t="inlineStr">
@@ -37496,12 +37720,12 @@
       </c>
       <c r="BC134" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD134" s="24" t="inlineStr">
         <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE134" s="24" t="inlineStr">
@@ -37516,12 +37740,12 @@
       </c>
       <c r="BG134" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH134" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:32.723645Z</t>
+          <t>2026-07-26T18:27:17.140917Z</t>
         </is>
       </c>
       <c r="BI134" s="24" t="inlineStr">
@@ -37531,13 +37755,13 @@
       </c>
       <c r="BJ134" s="25" t="n"/>
       <c r="BK134" s="26" t="n">
-        <v>156</v>
+        <v>-163</v>
       </c>
       <c r="BL134" s="27" t="n">
-        <v>2.56</v>
+        <v>1.613497</v>
       </c>
       <c r="BM134" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.619772</v>
       </c>
       <c r="BN134" s="28" t="n"/>
       <c r="BO134" s="28" t="n"/>
@@ -37571,37 +37795,37 @@
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="24" t="inlineStr">
         <is>
-          <t>4046eb4e53f148c0</t>
+          <t>a49cb48db1cd4164</t>
         </is>
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:45.242095Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C135" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T18:00:00Z</t>
+          <t>2026-07-27T17:30:00Z</t>
         </is>
       </c>
       <c r="D135" s="24" t="inlineStr">
         <is>
-          <t>60215</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="E135" s="24" t="inlineStr">
         <is>
-          <t>VALORANT</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F135" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="G135" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="H135" s="24" t="inlineStr">
@@ -37611,7 +37835,7 @@
       </c>
       <c r="I135" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J135" s="25" t="n"/>
@@ -37621,30 +37845,30 @@
         </is>
       </c>
       <c r="L135" s="26" t="n">
-        <v>-133</v>
+        <v>-156</v>
       </c>
       <c r="M135" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.641026</v>
       </c>
       <c r="N135" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.609375</v>
       </c>
       <c r="O135" s="28" t="n">
-        <v>0.5200050000000001</v>
+        <v>0.55859</v>
       </c>
       <c r="P135" s="28" t="n"/>
       <c r="Q135" s="28" t="n">
-        <v>-0.05081</v>
+        <v>-0.050785</v>
       </c>
       <c r="R135" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S135" s="29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T135" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U135" s="24" t="inlineStr">
@@ -37663,7 +37887,7 @@
       <c r="AD135" s="24" t="n"/>
       <c r="AE135" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-th-kc-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-navij-mouzn-2026-07-27).</t>
         </is>
       </c>
       <c r="AF135" s="31" t="inlineStr">
@@ -37681,7 +37905,7 @@
       <c r="AJ135" s="31" t="n"/>
       <c r="AK135" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL135" s="26" t="n">
@@ -37689,47 +37913,47 @@
       </c>
       <c r="AM135" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN135" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO135" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP135" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AQ135" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AR135" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AS135" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AT135" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AU135" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AV135" s="24" t="n"/>
@@ -37747,7 +37971,7 @@
       </c>
       <c r="BA135" s="24" t="inlineStr">
         <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB135" s="24" t="inlineStr">
@@ -37757,12 +37981,12 @@
       </c>
       <c r="BC135" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD135" s="24" t="inlineStr">
         <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE135" s="24" t="inlineStr">
@@ -37777,12 +38001,12 @@
       </c>
       <c r="BG135" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH135" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:33.517126Z</t>
+          <t>2026-07-26T18:27:17.612784Z</t>
         </is>
       </c>
       <c r="BI135" s="24" t="inlineStr">
@@ -37792,13 +38016,13 @@
       </c>
       <c r="BJ135" s="25" t="n"/>
       <c r="BK135" s="26" t="n">
-        <v>-133</v>
+        <v>-156</v>
       </c>
       <c r="BL135" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.641026</v>
       </c>
       <c r="BM135" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.609375</v>
       </c>
       <c r="BN135" s="28" t="n"/>
       <c r="BO135" s="28" t="n"/>
@@ -37832,37 +38056,37 @@
     <row r="136" ht="36" customHeight="1">
       <c r="A136" s="24" t="inlineStr">
         <is>
-          <t>bb38fcbac18948cb</t>
+          <t>9f88a21ac70f43af</t>
         </is>
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:45.242095Z</t>
+          <t>2026-07-26T18:27:27.249192Z</t>
         </is>
       </c>
       <c r="C136" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00Z</t>
+          <t>2026-07-27T12:00:00Z</t>
         </is>
       </c>
       <c r="D136" s="24" t="inlineStr">
         <is>
-          <t>60760</t>
+          <t>62511</t>
         </is>
       </c>
       <c r="E136" s="24" t="inlineStr">
         <is>
-          <t>VALORANT</t>
+          <t>DOTA2</t>
         </is>
       </c>
       <c r="F136" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Nemiga Gaming</t>
         </is>
       </c>
       <c r="G136" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr">
@@ -37882,30 +38106,30 @@
         </is>
       </c>
       <c r="L136" s="26" t="n">
-        <v>127</v>
+        <v>-117</v>
       </c>
       <c r="M136" s="27" t="n">
-        <v>2.27</v>
+        <v>1.854701</v>
       </c>
       <c r="N136" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.539171</v>
       </c>
       <c r="O136" s="28" t="n">
-        <v>0.5200050000000001</v>
+        <v>0.521452</v>
       </c>
       <c r="P136" s="28" t="n"/>
       <c r="Q136" s="28" t="n">
-        <v>0.079476</v>
+        <v>-0.017719</v>
       </c>
       <c r="R136" s="26" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="S136" s="29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T136" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U136" s="24" t="inlineStr">
@@ -37924,7 +38148,7 @@
       <c r="AD136" s="24" t="n"/>
       <c r="AE136" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-valorant-beg-hbs-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-stx-nemiga-2026-07-27).</t>
         </is>
       </c>
       <c r="AF136" s="31" t="inlineStr">
@@ -37942,7 +38166,7 @@
       <c r="AJ136" s="31" t="n"/>
       <c r="AK136" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL136" s="26" t="n">
@@ -37950,47 +38174,47 @@
       </c>
       <c r="AM136" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN136" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO136" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP136" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Nemiga Gaming</t>
         </is>
       </c>
       <c r="AQ136" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Nemiga Gaming</t>
         </is>
       </c>
       <c r="AR136" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Nemiga Gaming</t>
         </is>
       </c>
       <c r="AS136" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AT136" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AU136" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AV136" s="24" t="n"/>
@@ -38008,7 +38232,7 @@
       </c>
       <c r="BA136" s="24" t="inlineStr">
         <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
         </is>
       </c>
       <c r="BB136" s="24" t="inlineStr">
@@ -38018,12 +38242,12 @@
       </c>
       <c r="BC136" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD136" s="24" t="inlineStr">
         <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
         </is>
       </c>
       <c r="BE136" s="24" t="inlineStr">
@@ -38038,12 +38262,12 @@
       </c>
       <c r="BG136" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH136" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:35.966755Z</t>
+          <t>2026-07-26T18:27:26.048236Z</t>
         </is>
       </c>
       <c r="BI136" s="24" t="inlineStr">
@@ -38053,13 +38277,13 @@
       </c>
       <c r="BJ136" s="25" t="n"/>
       <c r="BK136" s="26" t="n">
-        <v>127</v>
+        <v>-117</v>
       </c>
       <c r="BL136" s="27" t="n">
-        <v>2.27</v>
+        <v>1.854701</v>
       </c>
       <c r="BM136" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.539171</v>
       </c>
       <c r="BN136" s="28" t="n"/>
       <c r="BO136" s="28" t="n"/>
@@ -38090,6 +38314,789 @@
       <c r="CN136" s="24" t="n"/>
       <c r="CO136" s="24" t="n"/>
     </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="24" t="inlineStr">
+        <is>
+          <t>2a34c43718e84671</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:27:27.249192Z</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D137" s="24" t="inlineStr">
+        <is>
+          <t>62512</t>
+        </is>
+      </c>
+      <c r="E137" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="H137" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I137" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J137" s="25" t="n"/>
+      <c r="K137" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M137" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N137" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O137" s="28" t="n">
+        <v>0.521452</v>
+      </c>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="28" t="n">
+        <v>-0.049363</v>
+      </c>
+      <c r="R137" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U137" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="n"/>
+      <c r="W137" s="26" t="n"/>
+      <c r="X137" s="26" t="n"/>
+      <c r="Y137" s="25" t="n"/>
+      <c r="Z137" s="26" t="n"/>
+      <c r="AA137" s="28" t="n"/>
+      <c r="AB137" s="28" t="n"/>
+      <c r="AC137" s="30" t="n"/>
+      <c r="AD137" s="24" t="n"/>
+      <c r="AE137" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-tje-ill-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF137" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG137" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH137" s="24" t="n"/>
+      <c r="AI137" s="31" t="n"/>
+      <c r="AJ137" s="31" t="n"/>
+      <c r="AK137" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL137" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM137" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN137" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO137" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP137" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AQ137" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AR137" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AS137" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AT137" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AU137" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AV137" s="24" t="n"/>
+      <c r="AW137" s="24" t="n"/>
+      <c r="AX137" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY137" s="24" t="n"/>
+      <c r="AZ137" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA137" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BB137" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC137" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD137" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BE137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG137" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH137" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:27:26.682922Z</t>
+        </is>
+      </c>
+      <c r="BI137" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ137" s="25" t="n"/>
+      <c r="BK137" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL137" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM137" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN137" s="28" t="n"/>
+      <c r="BO137" s="28" t="n"/>
+      <c r="BP137" s="25" t="n"/>
+      <c r="BQ137" s="27" t="n"/>
+      <c r="BR137" s="28" t="n"/>
+      <c r="BS137" s="28" t="n"/>
+      <c r="BT137" s="28" t="n"/>
+      <c r="BU137" s="25" t="n"/>
+      <c r="BV137" s="29" t="n"/>
+      <c r="BW137" s="24" t="n"/>
+      <c r="BX137" s="30" t="n"/>
+      <c r="BY137" s="27" t="n"/>
+      <c r="BZ137" s="24" t="n"/>
+      <c r="CA137" s="31" t="n"/>
+      <c r="CB137" s="24" t="n"/>
+      <c r="CC137" s="24" t="n"/>
+      <c r="CD137" s="24" t="n"/>
+      <c r="CE137" s="24" t="n"/>
+      <c r="CF137" s="24" t="n"/>
+      <c r="CG137" s="24" t="n"/>
+      <c r="CH137" s="24" t="n"/>
+      <c r="CI137" s="24" t="n"/>
+      <c r="CJ137" s="24" t="n"/>
+      <c r="CK137" s="24" t="n"/>
+      <c r="CL137" s="24" t="n"/>
+      <c r="CM137" s="24" t="n"/>
+      <c r="CN137" s="24" t="n"/>
+      <c r="CO137" s="24" t="n"/>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="24" t="inlineStr">
+        <is>
+          <t>0bd94a90d29f4021</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:27:27.249192Z</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D138" s="24" t="inlineStr">
+        <is>
+          <t>62513</t>
+        </is>
+      </c>
+      <c r="E138" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="H138" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I138" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J138" s="25" t="n"/>
+      <c r="K138" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L138" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M138" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N138" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O138" s="28" t="n">
+        <v>0.521452</v>
+      </c>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="28" t="n">
+        <v>-0.178248</v>
+      </c>
+      <c r="R138" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U138" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="n"/>
+      <c r="W138" s="26" t="n"/>
+      <c r="X138" s="26" t="n"/>
+      <c r="Y138" s="25" t="n"/>
+      <c r="Z138" s="26" t="n"/>
+      <c r="AA138" s="28" t="n"/>
+      <c r="AB138" s="28" t="n"/>
+      <c r="AC138" s="30" t="n"/>
+      <c r="AD138" s="24" t="n"/>
+      <c r="AE138" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-bald-kw-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF138" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG138" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH138" s="24" t="n"/>
+      <c r="AI138" s="31" t="n"/>
+      <c r="AJ138" s="31" t="n"/>
+      <c r="AK138" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL138" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM138" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN138" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO138" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP138" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AQ138" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AR138" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AS138" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AT138" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AU138" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AV138" s="24" t="n"/>
+      <c r="AW138" s="24" t="n"/>
+      <c r="AX138" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY138" s="24" t="n"/>
+      <c r="AZ138" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA138" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BB138" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC138" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD138" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BE138" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF138" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG138" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH138" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:27:27.247049Z</t>
+        </is>
+      </c>
+      <c r="BI138" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ138" s="25" t="n"/>
+      <c r="BK138" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL138" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM138" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN138" s="28" t="n"/>
+      <c r="BO138" s="28" t="n"/>
+      <c r="BP138" s="25" t="n"/>
+      <c r="BQ138" s="27" t="n"/>
+      <c r="BR138" s="28" t="n"/>
+      <c r="BS138" s="28" t="n"/>
+      <c r="BT138" s="28" t="n"/>
+      <c r="BU138" s="25" t="n"/>
+      <c r="BV138" s="29" t="n"/>
+      <c r="BW138" s="24" t="n"/>
+      <c r="BX138" s="30" t="n"/>
+      <c r="BY138" s="27" t="n"/>
+      <c r="BZ138" s="24" t="n"/>
+      <c r="CA138" s="31" t="n"/>
+      <c r="CB138" s="24" t="n"/>
+      <c r="CC138" s="24" t="n"/>
+      <c r="CD138" s="24" t="n"/>
+      <c r="CE138" s="24" t="n"/>
+      <c r="CF138" s="24" t="n"/>
+      <c r="CG138" s="24" t="n"/>
+      <c r="CH138" s="24" t="n"/>
+      <c r="CI138" s="24" t="n"/>
+      <c r="CJ138" s="24" t="n"/>
+      <c r="CK138" s="24" t="n"/>
+      <c r="CL138" s="24" t="n"/>
+      <c r="CM138" s="24" t="n"/>
+      <c r="CN138" s="24" t="n"/>
+      <c r="CO138" s="24" t="n"/>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="24" t="inlineStr">
+        <is>
+          <t>e1a99bb0c05843b8</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:27:38.719145Z</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D139" s="24" t="inlineStr">
+        <is>
+          <t>60760</t>
+        </is>
+      </c>
+      <c r="E139" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="H139" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I139" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J139" s="25" t="n"/>
+      <c r="K139" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L139" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M139" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N139" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O139" s="28" t="n">
+        <v>0.5200050000000001</v>
+      </c>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="28" t="n">
+        <v>0.06955500000000001</v>
+      </c>
+      <c r="R139" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S139" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U139" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="n"/>
+      <c r="W139" s="26" t="n"/>
+      <c r="X139" s="26" t="n"/>
+      <c r="Y139" s="25" t="n"/>
+      <c r="Z139" s="26" t="n"/>
+      <c r="AA139" s="28" t="n"/>
+      <c r="AB139" s="28" t="n"/>
+      <c r="AC139" s="30" t="n"/>
+      <c r="AD139" s="24" t="n"/>
+      <c r="AE139" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-beg-hbs-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF139" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG139" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH139" s="24" t="n"/>
+      <c r="AI139" s="31" t="n"/>
+      <c r="AJ139" s="31" t="n"/>
+      <c r="AK139" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL139" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM139" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN139" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO139" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP139" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ139" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR139" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS139" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AT139" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AU139" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AV139" s="24" t="n"/>
+      <c r="AW139" s="24" t="n"/>
+      <c r="AX139" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY139" s="24" t="n"/>
+      <c r="AZ139" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA139" s="24" t="inlineStr">
+        <is>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+        </is>
+      </c>
+      <c r="BB139" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC139" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD139" s="24" t="inlineStr">
+        <is>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
+        </is>
+      </c>
+      <c r="BE139" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF139" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG139" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH139" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:27:32.117632Z</t>
+        </is>
+      </c>
+      <c r="BI139" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ139" s="25" t="n"/>
+      <c r="BK139" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL139" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM139" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN139" s="28" t="n"/>
+      <c r="BO139" s="28" t="n"/>
+      <c r="BP139" s="25" t="n"/>
+      <c r="BQ139" s="27" t="n"/>
+      <c r="BR139" s="28" t="n"/>
+      <c r="BS139" s="28" t="n"/>
+      <c r="BT139" s="28" t="n"/>
+      <c r="BU139" s="25" t="n"/>
+      <c r="BV139" s="29" t="n"/>
+      <c r="BW139" s="24" t="n"/>
+      <c r="BX139" s="30" t="n"/>
+      <c r="BY139" s="27" t="n"/>
+      <c r="BZ139" s="24" t="n"/>
+      <c r="CA139" s="31" t="n"/>
+      <c r="CB139" s="24" t="n"/>
+      <c r="CC139" s="24" t="n"/>
+      <c r="CD139" s="24" t="n"/>
+      <c r="CE139" s="24" t="n"/>
+      <c r="CF139" s="24" t="n"/>
+      <c r="CG139" s="24" t="n"/>
+      <c r="CH139" s="24" t="n"/>
+      <c r="CI139" s="24" t="n"/>
+      <c r="CJ139" s="24" t="n"/>
+      <c r="CK139" s="24" t="n"/>
+      <c r="CL139" s="24" t="n"/>
+      <c r="CM139" s="24" t="n"/>
+      <c r="CN139" s="24" t="n"/>
+      <c r="CO139" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
